--- a/model/CVR_Model_Phase2_Forecast.xlsx
+++ b/model/CVR_Model_Phase2_Forecast.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Backlog &amp; Pipeline" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="FY Summary" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Checks" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Coverage Chart" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -104,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,6 +133,8 @@
     <xf numFmtId="167" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -206,6 +209,215 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Forecast revenue vs booked backlog + weighted pipeline ($K/month)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <areaChart>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Coverage Chart'!A34</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9EC5F4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Coverage Chart'!$B$24:$S$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Coverage Chart'!$B$34:$S$34</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Coverage Chart'!A40</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="CDE2FB"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Coverage Chart'!$B$24:$S$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Coverage Chart'!$B$40:$S$40</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </areaChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Coverage Chart'!A41</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Coverage Chart'!$B$24:$S$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Coverage Chart'!$B$41:$S$41</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="200"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="250"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$K per month</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="200"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="250"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -497,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -646,10 +858,24 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coverage Chart     — native chart: forecast line vs backlog + pipeline areas, with a 1/0 toggle</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       cell (B3) that includes or excludes the weighted pipeline live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>COLOR KEY: blue = input · black = calculated · orange italics = assumption to confirm</t>
         </is>
@@ -5010,4 +5236,1387 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast &amp; work coverage — with pipeline toggle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Native chart wired to live cells. Set the toggle to 0 to see booked backlog only; edit job remainders or bid probabilities and everything redraws.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Include weighted pipeline? (1 = yes, 0 = no)</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Coverage of forecast</t>
+        </is>
+      </c>
+      <c r="B5" s="25">
+        <f>(SUM(B34:S34)+SUM(B40:S40))/SUM(B41:S41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gap to originate ($K)</t>
+        </is>
+      </c>
+      <c r="B6" s="26">
+        <f>SUM(B41:S41)-SUM(B34:S34)-SUM(B40:S40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>CHART DATA ($K/month) — formulas reference Backlog &amp; Pipeline and Forecast P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Oct-26</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nov-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dec-26</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Jan-27</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Feb-27</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Mar-27</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Apr-27</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>May-27</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Jun-27</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Jul-27</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Aug-27</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sep-27</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Oct-27</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Nov-27</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Dec-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>burn: DTE — Catalina Conversion Ph 3</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="D25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="E25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="F25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>burn: DTE — New Baltimore Conversion</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="E26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="F26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="J26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="K26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="L26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="M26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="N26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="O26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="P26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="Q26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="R26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="S26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>burn: Consumers — 2026 HVD Line Sensors</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>'Backlog &amp; Pipeline'!$E7/4</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>'Backlog &amp; Pipeline'!$E7/4</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>'Backlog &amp; Pipeline'!$E7/4</f>
+        <v/>
+      </c>
+      <c r="E27">
+        <f>'Backlog &amp; Pipeline'!$E7/4</f>
+        <v/>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>burn: Cloverland — Manistique Pump Stn</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>'Backlog &amp; Pipeline'!$E8/3</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>'Backlog &amp; Pipeline'!$E8/3</f>
+        <v/>
+      </c>
+      <c r="D28">
+        <f>'Backlog &amp; Pipeline'!$E8/3</f>
+        <v/>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Gateway 69kV</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>'Backlog &amp; Pipeline'!$E9/2</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>'Backlog &amp; Pipeline'!$E9/2</f>
+        <v/>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Rockport 69kV</t>
+        </is>
+      </c>
+      <c r="B30">
+        <f>'Backlog &amp; Pipeline'!$E10/2</f>
+        <v/>
+      </c>
+      <c r="C30">
+        <f>'Backlog &amp; Pipeline'!$E10/2</f>
+        <v/>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Angel Mounds 69kV</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>'Backlog &amp; Pipeline'!$E11/4</f>
+        <v/>
+      </c>
+      <c r="C31">
+        <f>'Backlog &amp; Pipeline'!$E11/4</f>
+        <v/>
+      </c>
+      <c r="D31">
+        <f>'Backlog &amp; Pipeline'!$E11/4</f>
+        <v/>
+      </c>
+      <c r="E31">
+        <f>'Backlog &amp; Pipeline'!$E11/4</f>
+        <v/>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Northwest 69kV</t>
+        </is>
+      </c>
+      <c r="B32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="C32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="E32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="F32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="H32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="I32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="J32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="K32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="L32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="M32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="N32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="O32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Leonard Rd 69kV</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="C33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="D33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="E33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="F33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="I33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="J33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="K33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="L33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="M33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="O33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="P33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="Q33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Booked backlog</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>SUM(B25:B33)</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>SUM(C25:C33)</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>SUM(D25:D33)</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>SUM(E25:E33)</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>SUM(F25:F33)</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>SUM(G25:G33)</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>SUM(H25:H33)</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>SUM(I25:I33)</f>
+        <v/>
+      </c>
+      <c r="J34">
+        <f>SUM(J25:J33)</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>SUM(K25:K33)</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>SUM(L25:L33)</f>
+        <v/>
+      </c>
+      <c r="M34">
+        <f>SUM(M25:M33)</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>SUM(N25:N33)</f>
+        <v/>
+      </c>
+      <c r="O34">
+        <f>SUM(O25:O33)</f>
+        <v/>
+      </c>
+      <c r="P34">
+        <f>SUM(P25:P33)</f>
+        <v/>
+      </c>
+      <c r="Q34">
+        <f>SUM(Q25:Q33)</f>
+        <v/>
+      </c>
+      <c r="R34">
+        <f>SUM(R25:R33)</f>
+        <v/>
+      </c>
+      <c r="S34">
+        <f>SUM(S25:S33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>bid: Frontier Make Ready</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="E35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="H35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="I35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>bid: Jacksonburg–Gateway (EPC-paired $3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="H36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="I36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="J36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="K36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="L36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="M36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="O36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="P36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="Q36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>bid: Rosehill–Rockport (EPC-paired $5.5</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="I37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="J37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="K37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="L37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="M37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="O37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="P37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="Q37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>bid: Joint Use Audit</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="H38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="I38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="J38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="K38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="L38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="M38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="N38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="O38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="P38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="Q38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="R38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="S38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>bid: 2026 Pole Replacements (EPC-paired</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="H39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="I39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="J39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="L39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="M39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="N39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="O39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="P39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="Q39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Weighted pipeline (× toggle)</t>
+        </is>
+      </c>
+      <c r="B40">
+        <f>SUM(B35:B39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="C40">
+        <f>SUM(C35:C39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="D40">
+        <f>SUM(D35:D39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="E40">
+        <f>SUM(E35:E39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="F40">
+        <f>SUM(F35:F39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>SUM(G35:G39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="H40">
+        <f>SUM(H35:H39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="I40">
+        <f>SUM(I35:I39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="J40">
+        <f>SUM(J35:J39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>SUM(K35:K39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="L40">
+        <f>SUM(L35:L39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="M40">
+        <f>SUM(M35:M39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="N40">
+        <f>SUM(N35:N39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="O40">
+        <f>SUM(O35:O39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="P40">
+        <f>SUM(P35:P39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="Q40">
+        <f>SUM(Q35:Q39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="R40">
+        <f>SUM(R35:R39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="S40">
+        <f>SUM(S35:S39)*$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Forecast revenue</t>
+        </is>
+      </c>
+      <c r="B41">
+        <f>'Forecast P&amp;L'!B6</f>
+        <v/>
+      </c>
+      <c r="C41">
+        <f>'Forecast P&amp;L'!C6</f>
+        <v/>
+      </c>
+      <c r="D41">
+        <f>'Forecast P&amp;L'!D6</f>
+        <v/>
+      </c>
+      <c r="E41">
+        <f>'Forecast P&amp;L'!E6</f>
+        <v/>
+      </c>
+      <c r="F41">
+        <f>'Forecast P&amp;L'!F6</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>'Forecast P&amp;L'!G6</f>
+        <v/>
+      </c>
+      <c r="H41">
+        <f>'Forecast P&amp;L'!H6</f>
+        <v/>
+      </c>
+      <c r="I41">
+        <f>'Forecast P&amp;L'!I6</f>
+        <v/>
+      </c>
+      <c r="J41">
+        <f>'Forecast P&amp;L'!J6</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>'Forecast P&amp;L'!K6</f>
+        <v/>
+      </c>
+      <c r="L41">
+        <f>'Forecast P&amp;L'!L6</f>
+        <v/>
+      </c>
+      <c r="M41">
+        <f>'Forecast P&amp;L'!M6</f>
+        <v/>
+      </c>
+      <c r="N41">
+        <f>'Forecast P&amp;L'!N6</f>
+        <v/>
+      </c>
+      <c r="O41">
+        <f>'Forecast P&amp;L'!O6</f>
+        <v/>
+      </c>
+      <c r="P41">
+        <f>'Forecast P&amp;L'!P6</f>
+        <v/>
+      </c>
+      <c r="Q41">
+        <f>'Forecast P&amp;L'!Q6</f>
+        <v/>
+      </c>
+      <c r="R41">
+        <f>'Forecast P&amp;L'!R6</f>
+        <v/>
+      </c>
+      <c r="S41">
+        <f>'Forecast P&amp;L'!S6</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/model/CVR_Model_Phase2_Forecast.xlsx
+++ b/model/CVR_Model_Phase2_Forecast.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scenario Paths" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Drivers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Forecast P&amp;L" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cash &amp; Note" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Backlog &amp; Pipeline" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="FY Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Checks" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Coverage Chart" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario Paths" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drivers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast P&amp;L" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vs Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash &amp; Note" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog &amp; Pipeline" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FY Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Chart" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -105,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,8 +131,9 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,13 +214,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -241,10 +243,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9EC5F4"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -268,10 +270,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="CDE2FB"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -300,7 +302,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -310,7 +312,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -353,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -394,7 +396,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -409,9 +411,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -709,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -832,50 +834,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash &amp; Note        — AR, operating cash, and the parent-note roll-forward (funds every deficit).</t>
+          <t xml:space="preserve">  vs Budget          — forecast vs finance's 2026 monthly budget, line by line (H2-2026).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Backlog &amp; Pipeline — remaining value on active jobs + probability-weighted bids; coverage check.</t>
+          <t xml:space="preserve">  Cash &amp; Note        — AR, operating cash, and the parent-note roll-forward (funds every deficit).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FY Summary         — FY2026 landing (H1 actual + H2 forecast) vs budget; FY2027 vs the $6M goal.</t>
+          <t xml:space="preserve">  Backlog &amp; Pipeline — remaining value on active jobs + probability-weighted bids; coverage check.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Checks             — anchors to the GL baseline and internal integrity checks.</t>
+          <t xml:space="preserve">  FY Summary         — FY2026 landing (H1 actual + H2 forecast) vs budget; FY2027 vs the $6M goal.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Coverage Chart     — native chart: forecast line vs backlog + pipeline areas, with a 1/0 toggle</t>
+          <t xml:space="preserve">  Checks             — anchors to the GL baseline and internal integrity checks.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Coverage Chart     — native chart: forecast line vs backlog + pipeline areas, with a 1/0 toggle</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t xml:space="preserve">                       cell (B3) that includes or excludes the weighted pipeline live.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>COLOR KEY: blue = input · black = calculated · orange italics = assumption to confirm</t>
         </is>
@@ -883,6 +892,1389 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast &amp; work coverage — with pipeline toggle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Native chart wired to live cells. Set the toggle to 0 to see booked backlog only; edit job remainders or bid probabilities and everything redraws.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Include weighted pipeline? (1 = yes, 0 = no)</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Coverage of forecast</t>
+        </is>
+      </c>
+      <c r="B5" s="26">
+        <f>(SUM(B34:S34)+SUM(B40:S40))/SUM(B41:S41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gap to originate ($K)</t>
+        </is>
+      </c>
+      <c r="B6" s="27">
+        <f>SUM(B41:S41)-SUM(B34:S34)-SUM(B40:S40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>CHART DATA ($K/month) — formulas reference Backlog &amp; Pipeline and Forecast P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Oct-26</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nov-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dec-26</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Jan-27</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Feb-27</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Mar-27</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Apr-27</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>May-27</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Jun-27</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Jul-27</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Aug-27</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sep-27</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Oct-27</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Nov-27</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Dec-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>burn: DTE — Catalina Conversion Ph 3</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="D25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="E25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="F25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>'Backlog &amp; Pipeline'!$E5/6</f>
+        <v/>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>burn: DTE — New Baltimore Conversion</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="D26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="E26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="F26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="J26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="K26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="L26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="M26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="N26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="O26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="P26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="Q26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="R26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+      <c r="S26">
+        <f>'Backlog &amp; Pipeline'!$E6/18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>burn: Consumers — 2026 HVD Line Sensors</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>'Backlog &amp; Pipeline'!$E7/4</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>'Backlog &amp; Pipeline'!$E7/4</f>
+        <v/>
+      </c>
+      <c r="D27">
+        <f>'Backlog &amp; Pipeline'!$E7/4</f>
+        <v/>
+      </c>
+      <c r="E27">
+        <f>'Backlog &amp; Pipeline'!$E7/4</f>
+        <v/>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>burn: Cloverland — Manistique Pump Stn</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>'Backlog &amp; Pipeline'!$E8/3</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>'Backlog &amp; Pipeline'!$E8/3</f>
+        <v/>
+      </c>
+      <c r="D28">
+        <f>'Backlog &amp; Pipeline'!$E8/3</f>
+        <v/>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Gateway 69kV</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>'Backlog &amp; Pipeline'!$E9/2</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>'Backlog &amp; Pipeline'!$E9/2</f>
+        <v/>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Rockport 69kV</t>
+        </is>
+      </c>
+      <c r="B30">
+        <f>'Backlog &amp; Pipeline'!$E10/2</f>
+        <v/>
+      </c>
+      <c r="C30">
+        <f>'Backlog &amp; Pipeline'!$E10/2</f>
+        <v/>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Angel Mounds 69kV</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>'Backlog &amp; Pipeline'!$E11/4</f>
+        <v/>
+      </c>
+      <c r="C31">
+        <f>'Backlog &amp; Pipeline'!$E11/4</f>
+        <v/>
+      </c>
+      <c r="D31">
+        <f>'Backlog &amp; Pipeline'!$E11/4</f>
+        <v/>
+      </c>
+      <c r="E31">
+        <f>'Backlog &amp; Pipeline'!$E11/4</f>
+        <v/>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Northwest 69kV</t>
+        </is>
+      </c>
+      <c r="B32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="C32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="E32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="F32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="H32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="I32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="J32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="K32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="L32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="M32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="N32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="O32">
+        <f>'Backlog &amp; Pipeline'!$E12/14</f>
+        <v/>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>burn: CenterPoint — Leonard Rd 69kV</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="C33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="D33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="E33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="F33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="I33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="J33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="K33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="L33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="M33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="O33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="P33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="Q33">
+        <f>'Backlog &amp; Pipeline'!$E13/16</f>
+        <v/>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Booked backlog</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>SUM(B25:B33)</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>SUM(C25:C33)</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>SUM(D25:D33)</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>SUM(E25:E33)</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>SUM(F25:F33)</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>SUM(G25:G33)</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>SUM(H25:H33)</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>SUM(I25:I33)</f>
+        <v/>
+      </c>
+      <c r="J34">
+        <f>SUM(J25:J33)</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>SUM(K25:K33)</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>SUM(L25:L33)</f>
+        <v/>
+      </c>
+      <c r="M34">
+        <f>SUM(M25:M33)</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>SUM(N25:N33)</f>
+        <v/>
+      </c>
+      <c r="O34">
+        <f>SUM(O25:O33)</f>
+        <v/>
+      </c>
+      <c r="P34">
+        <f>SUM(P25:P33)</f>
+        <v/>
+      </c>
+      <c r="Q34">
+        <f>SUM(Q25:Q33)</f>
+        <v/>
+      </c>
+      <c r="R34">
+        <f>SUM(R25:R33)</f>
+        <v/>
+      </c>
+      <c r="S34">
+        <f>SUM(S25:S33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>bid: Frontier Make Ready</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="E35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="H35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="I35">
+        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <v/>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>bid: Jacksonburg–Gateway (EPC-paired $3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="H36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="I36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="J36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="K36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="L36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="M36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="N36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="O36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="P36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="Q36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <v/>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>bid: Rosehill–Rockport (EPC-paired $5.5</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="I37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="J37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="K37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="L37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="M37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="N37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="O37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="P37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="Q37">
+        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
+        <v/>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>bid: Joint Use Audit</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="H38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="I38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="J38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="K38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="L38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="M38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="N38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="O38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="P38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="Q38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="R38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+      <c r="S38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>bid: 2026 Pole Replacements (EPC-paired</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="H39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="I39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="J39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="L39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="M39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="N39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="O39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="P39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="Q39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <v/>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Weighted pipeline (× toggle)</t>
+        </is>
+      </c>
+      <c r="B40">
+        <f>SUM(B35:B39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="C40">
+        <f>SUM(C35:C39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="D40">
+        <f>SUM(D35:D39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="E40">
+        <f>SUM(E35:E39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="F40">
+        <f>SUM(F35:F39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>SUM(G35:G39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="H40">
+        <f>SUM(H35:H39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="I40">
+        <f>SUM(I35:I39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="J40">
+        <f>SUM(J35:J39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>SUM(K35:K39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="L40">
+        <f>SUM(L35:L39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="M40">
+        <f>SUM(M35:M39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="N40">
+        <f>SUM(N35:N39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="O40">
+        <f>SUM(O35:O39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="P40">
+        <f>SUM(P35:P39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="Q40">
+        <f>SUM(Q35:Q39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="R40">
+        <f>SUM(R35:R39)*$B$3</f>
+        <v/>
+      </c>
+      <c r="S40">
+        <f>SUM(S35:S39)*$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Forecast revenue</t>
+        </is>
+      </c>
+      <c r="B41">
+        <f>'Forecast P&amp;L'!B6</f>
+        <v/>
+      </c>
+      <c r="C41">
+        <f>'Forecast P&amp;L'!C6</f>
+        <v/>
+      </c>
+      <c r="D41">
+        <f>'Forecast P&amp;L'!D6</f>
+        <v/>
+      </c>
+      <c r="E41">
+        <f>'Forecast P&amp;L'!E6</f>
+        <v/>
+      </c>
+      <c r="F41">
+        <f>'Forecast P&amp;L'!F6</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>'Forecast P&amp;L'!G6</f>
+        <v/>
+      </c>
+      <c r="H41">
+        <f>'Forecast P&amp;L'!H6</f>
+        <v/>
+      </c>
+      <c r="I41">
+        <f>'Forecast P&amp;L'!I6</f>
+        <v/>
+      </c>
+      <c r="J41">
+        <f>'Forecast P&amp;L'!J6</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>'Forecast P&amp;L'!K6</f>
+        <v/>
+      </c>
+      <c r="L41">
+        <f>'Forecast P&amp;L'!L6</f>
+        <v/>
+      </c>
+      <c r="M41">
+        <f>'Forecast P&amp;L'!M6</f>
+        <v/>
+      </c>
+      <c r="N41">
+        <f>'Forecast P&amp;L'!N6</f>
+        <v/>
+      </c>
+      <c r="O41">
+        <f>'Forecast P&amp;L'!O6</f>
+        <v/>
+      </c>
+      <c r="P41">
+        <f>'Forecast P&amp;L'!P6</f>
+        <v/>
+      </c>
+      <c r="Q41">
+        <f>'Forecast P&amp;L'!Q6</f>
+        <v/>
+      </c>
+      <c r="R41">
+        <f>'Forecast P&amp;L'!R6</f>
+        <v/>
+      </c>
+      <c r="S41">
+        <f>'Forecast P&amp;L'!S6</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1576,12 +2968,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1974,118 +3366,103 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Avg loaded wage per FTE-month ($)</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>7756</v>
+          <t>Direct-labor cost / billable hr ($)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>54.89</v>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>GL H1: $465.4K wages ÷ 6 mo ÷ 10 FTE</t>
+          <t>2026 Budget: $779.8K direct labor ÷ 14,205 billable hrs</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Direct-charge share of wages</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>0.92</v>
+          <t>Total loaded labor / FTE-month ($)</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>12189</v>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>GL H1: direct labor $428.5K of $465.4K total wages</t>
+          <t>2026 Budget: $1.422M total labor cost ÷ 9.72 budget FTE ÷ 12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Burden % of wages</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>0.338</v>
+          <t>Non-labor OpEx per month ($)</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>21748</v>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>GL H1 burden lines ÷ wages</t>
+          <t>2026 Budget: OpEx less all labor &amp; overhead, monthly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Other OpEx per month ($)</t>
+          <t>Corporate overhead per month ($)</t>
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>19193</v>
+        <v>17250</v>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>GL H1: OpEx less burden, overhead, indirect labor, ÷ 6</t>
+          <t>2026 Budget: $207K ÷ 12 (flat)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Corporate overhead per month ($)</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>17250</v>
+          <t>Interest rate on parent note (APR)</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>0.0175</v>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>GL: flat allocation</t>
+          <t>GL H1: $30.1K ÷ 6 ÷ $3.44M ×12 (budget assumes $0)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Interest rate on parent note (APR)</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>0.0175</v>
+          <t>DSO (days sales outstanding)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>46</v>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>GL H1: $30.1K ÷ 6 ÷ $3.44M ×12</t>
+          <t>GL: AR $139.8K vs H1 revenue</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>DSO (days sales outstanding)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>46</v>
+          <t>Available hours per FTE-month</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>173.33</v>
       </c>
       <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>GL: AR $139.8K vs H1 revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Available hours per FTE-month</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>173.33</v>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>2,080 ÷ 12</t>
         </is>
@@ -2256,75 +3633,75 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>Drivers!B$6*Drivers!$B$20*Drivers!B$7</f>
+        <f>Drivers!B$6*Drivers!$B$19*Drivers!B$7</f>
         <v/>
       </c>
       <c r="C5" s="17">
-        <f>Drivers!C$6*Drivers!$B$20*Drivers!C$7</f>
+        <f>Drivers!C$6*Drivers!$B$19*Drivers!C$7</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>Drivers!D$6*Drivers!$B$20*Drivers!D$7</f>
+        <f>Drivers!D$6*Drivers!$B$19*Drivers!D$7</f>
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>Drivers!E$6*Drivers!$B$20*Drivers!E$7</f>
+        <f>Drivers!E$6*Drivers!$B$19*Drivers!E$7</f>
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>Drivers!F$6*Drivers!$B$20*Drivers!F$7</f>
+        <f>Drivers!F$6*Drivers!$B$19*Drivers!F$7</f>
         <v/>
       </c>
       <c r="G5" s="17">
-        <f>Drivers!G$6*Drivers!$B$20*Drivers!G$7</f>
+        <f>Drivers!G$6*Drivers!$B$19*Drivers!G$7</f>
         <v/>
       </c>
       <c r="H5" s="17">
-        <f>Drivers!H$6*Drivers!$B$20*Drivers!H$7</f>
+        <f>Drivers!H$6*Drivers!$B$19*Drivers!H$7</f>
         <v/>
       </c>
       <c r="I5" s="17">
-        <f>Drivers!I$6*Drivers!$B$20*Drivers!I$7</f>
+        <f>Drivers!I$6*Drivers!$B$19*Drivers!I$7</f>
         <v/>
       </c>
       <c r="J5" s="17">
-        <f>Drivers!J$6*Drivers!$B$20*Drivers!J$7</f>
+        <f>Drivers!J$6*Drivers!$B$19*Drivers!J$7</f>
         <v/>
       </c>
       <c r="K5" s="17">
-        <f>Drivers!K$6*Drivers!$B$20*Drivers!K$7</f>
+        <f>Drivers!K$6*Drivers!$B$19*Drivers!K$7</f>
         <v/>
       </c>
       <c r="L5" s="17">
-        <f>Drivers!L$6*Drivers!$B$20*Drivers!L$7</f>
+        <f>Drivers!L$6*Drivers!$B$19*Drivers!L$7</f>
         <v/>
       </c>
       <c r="M5" s="17">
-        <f>Drivers!M$6*Drivers!$B$20*Drivers!M$7</f>
+        <f>Drivers!M$6*Drivers!$B$19*Drivers!M$7</f>
         <v/>
       </c>
       <c r="N5" s="17">
-        <f>Drivers!N$6*Drivers!$B$20*Drivers!N$7</f>
+        <f>Drivers!N$6*Drivers!$B$19*Drivers!N$7</f>
         <v/>
       </c>
       <c r="O5" s="17">
-        <f>Drivers!O$6*Drivers!$B$20*Drivers!O$7</f>
+        <f>Drivers!O$6*Drivers!$B$19*Drivers!O$7</f>
         <v/>
       </c>
       <c r="P5" s="17">
-        <f>Drivers!P$6*Drivers!$B$20*Drivers!P$7</f>
+        <f>Drivers!P$6*Drivers!$B$19*Drivers!P$7</f>
         <v/>
       </c>
       <c r="Q5" s="17">
-        <f>Drivers!Q$6*Drivers!$B$20*Drivers!Q$7</f>
+        <f>Drivers!Q$6*Drivers!$B$19*Drivers!Q$7</f>
         <v/>
       </c>
       <c r="R5" s="17">
-        <f>Drivers!R$6*Drivers!$B$20*Drivers!R$7</f>
+        <f>Drivers!R$6*Drivers!$B$19*Drivers!R$7</f>
         <v/>
       </c>
       <c r="S5" s="17">
-        <f>Drivers!S$6*Drivers!$B$20*Drivers!S$7</f>
+        <f>Drivers!S$6*Drivers!$B$19*Drivers!S$7</f>
         <v/>
       </c>
       <c r="T5" s="18">
@@ -2426,79 +3803,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Direct labor</t>
+          <t>Direct labor (billable hrs × budget rate)</t>
         </is>
       </c>
       <c r="B7" s="19">
-        <f>Drivers!B$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>B5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>Drivers!C$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>C5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="D7" s="19">
-        <f>Drivers!D$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>D5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="E7" s="19">
-        <f>Drivers!E$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>E5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="F7" s="19">
-        <f>Drivers!F$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>F5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="G7" s="19">
-        <f>Drivers!G$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>G5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="H7" s="19">
-        <f>Drivers!H$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>H5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="I7" s="19">
-        <f>Drivers!I$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>I5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="J7" s="19">
-        <f>Drivers!J$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>J5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="K7" s="19">
-        <f>Drivers!K$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>K5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="L7" s="19">
-        <f>Drivers!L$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>L5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="M7" s="19">
-        <f>Drivers!M$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>M5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="N7" s="19">
-        <f>Drivers!N$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>N5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="O7" s="19">
-        <f>Drivers!O$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>O5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="P7" s="19">
-        <f>Drivers!P$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>P5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="Q7" s="19">
-        <f>Drivers!Q$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>Q5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="R7" s="19">
-        <f>Drivers!R$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>R5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="S7" s="19">
-        <f>Drivers!S$6*Drivers!$B$13*Drivers!$B$14/1000</f>
+        <f>S5*Drivers!$B$13/1000</f>
         <v/>
       </c>
       <c r="T7" s="20">
@@ -2687,79 +4064,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Indirect labor</t>
+          <t>Indirect &amp; other labor (total labor − direct)</t>
         </is>
       </c>
       <c r="B10" s="19">
-        <f>Drivers!B$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!B$6*Drivers!$B$14/1000-B7</f>
         <v/>
       </c>
       <c r="C10" s="19">
-        <f>Drivers!C$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!C$6*Drivers!$B$14/1000-C7</f>
         <v/>
       </c>
       <c r="D10" s="19">
-        <f>Drivers!D$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!D$6*Drivers!$B$14/1000-D7</f>
         <v/>
       </c>
       <c r="E10" s="19">
-        <f>Drivers!E$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!E$6*Drivers!$B$14/1000-E7</f>
         <v/>
       </c>
       <c r="F10" s="19">
-        <f>Drivers!F$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!F$6*Drivers!$B$14/1000-F7</f>
         <v/>
       </c>
       <c r="G10" s="19">
-        <f>Drivers!G$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!G$6*Drivers!$B$14/1000-G7</f>
         <v/>
       </c>
       <c r="H10" s="19">
-        <f>Drivers!H$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!H$6*Drivers!$B$14/1000-H7</f>
         <v/>
       </c>
       <c r="I10" s="19">
-        <f>Drivers!I$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!I$6*Drivers!$B$14/1000-I7</f>
         <v/>
       </c>
       <c r="J10" s="19">
-        <f>Drivers!J$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!J$6*Drivers!$B$14/1000-J7</f>
         <v/>
       </c>
       <c r="K10" s="19">
-        <f>Drivers!K$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!K$6*Drivers!$B$14/1000-K7</f>
         <v/>
       </c>
       <c r="L10" s="19">
-        <f>Drivers!L$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!L$6*Drivers!$B$14/1000-L7</f>
         <v/>
       </c>
       <c r="M10" s="19">
-        <f>Drivers!M$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!M$6*Drivers!$B$14/1000-M7</f>
         <v/>
       </c>
       <c r="N10" s="19">
-        <f>Drivers!N$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!N$6*Drivers!$B$14/1000-N7</f>
         <v/>
       </c>
       <c r="O10" s="19">
-        <f>Drivers!O$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!O$6*Drivers!$B$14/1000-O7</f>
         <v/>
       </c>
       <c r="P10" s="19">
-        <f>Drivers!P$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!P$6*Drivers!$B$14/1000-P7</f>
         <v/>
       </c>
       <c r="Q10" s="19">
-        <f>Drivers!Q$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!Q$6*Drivers!$B$14/1000-Q7</f>
         <v/>
       </c>
       <c r="R10" s="19">
-        <f>Drivers!R$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!R$6*Drivers!$B$14/1000-R7</f>
         <v/>
       </c>
       <c r="S10" s="19">
-        <f>Drivers!S$6*Drivers!$B$13*(1-Drivers!$B$14)/1000</f>
+        <f>Drivers!S$6*Drivers!$B$14/1000-S7</f>
         <v/>
       </c>
       <c r="T10" s="20">
@@ -2774,79 +4151,79 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Burden (taxes, benefits, vac/hol)</t>
+          <t>Non-labor operating expenses</t>
         </is>
       </c>
       <c r="B11" s="19">
-        <f>Drivers!B$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="C11" s="19">
-        <f>Drivers!C$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="D11" s="19">
-        <f>Drivers!D$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="E11" s="19">
-        <f>Drivers!E$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="F11" s="19">
-        <f>Drivers!F$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="G11" s="19">
-        <f>Drivers!G$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="H11" s="19">
-        <f>Drivers!H$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="I11" s="19">
-        <f>Drivers!I$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="J11" s="19">
-        <f>Drivers!J$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="K11" s="19">
-        <f>Drivers!K$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="L11" s="19">
-        <f>Drivers!L$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="M11" s="19">
-        <f>Drivers!M$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="N11" s="19">
-        <f>Drivers!N$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="O11" s="19">
-        <f>Drivers!O$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="P11" s="19">
-        <f>Drivers!P$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="Q11" s="19">
-        <f>Drivers!Q$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="R11" s="19">
-        <f>Drivers!R$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="S11" s="19">
-        <f>Drivers!S$6*Drivers!$B$13*Drivers!$B$15/1000</f>
+        <f>Drivers!$B$15/1000</f>
         <v/>
       </c>
       <c r="T11" s="20">
@@ -2861,7 +4238,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Other operating expenses</t>
+          <t>Corporate overhead allocation</t>
         </is>
       </c>
       <c r="B12" s="19">
@@ -2946,81 +4323,81 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Corporate overhead allocation</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
         </is>
       </c>
       <c r="B13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(B10:B12)</f>
         <v/>
       </c>
       <c r="C13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(C10:C12)</f>
         <v/>
       </c>
       <c r="D13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(D10:D12)</f>
         <v/>
       </c>
       <c r="E13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(E10:E12)</f>
         <v/>
       </c>
       <c r="F13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(F10:F12)</f>
         <v/>
       </c>
       <c r="G13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(G10:G12)</f>
         <v/>
       </c>
       <c r="H13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(H10:H12)</f>
         <v/>
       </c>
       <c r="I13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(I10:I12)</f>
         <v/>
       </c>
       <c r="J13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(J10:J12)</f>
         <v/>
       </c>
       <c r="K13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(K10:K12)</f>
         <v/>
       </c>
       <c r="L13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(L10:L12)</f>
         <v/>
       </c>
       <c r="M13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(M10:M12)</f>
         <v/>
       </c>
       <c r="N13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(N10:N12)</f>
         <v/>
       </c>
       <c r="O13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(O10:O12)</f>
         <v/>
       </c>
       <c r="P13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(P10:P12)</f>
         <v/>
       </c>
       <c r="Q13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(Q10:Q12)</f>
         <v/>
       </c>
       <c r="R13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(R10:R12)</f>
         <v/>
       </c>
       <c r="S13" s="19">
-        <f>Drivers!$B$17/1000</f>
+        <f>SUM(S10:S12)</f>
         <v/>
       </c>
       <c r="T13" s="20">
@@ -3035,79 +4412,79 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Total Operating Expenses</t>
+          <t>Operating Income / (Loss)</t>
         </is>
       </c>
       <c r="B14" s="19">
-        <f>SUM(B10:B13)</f>
+        <f>B8-B13</f>
         <v/>
       </c>
       <c r="C14" s="19">
-        <f>SUM(C10:C13)</f>
+        <f>C8-C13</f>
         <v/>
       </c>
       <c r="D14" s="19">
-        <f>SUM(D10:D13)</f>
+        <f>D8-D13</f>
         <v/>
       </c>
       <c r="E14" s="19">
-        <f>SUM(E10:E13)</f>
+        <f>E8-E13</f>
         <v/>
       </c>
       <c r="F14" s="19">
-        <f>SUM(F10:F13)</f>
+        <f>F8-F13</f>
         <v/>
       </c>
       <c r="G14" s="19">
-        <f>SUM(G10:G13)</f>
+        <f>G8-G13</f>
         <v/>
       </c>
       <c r="H14" s="19">
-        <f>SUM(H10:H13)</f>
+        <f>H8-H13</f>
         <v/>
       </c>
       <c r="I14" s="19">
-        <f>SUM(I10:I13)</f>
+        <f>I8-I13</f>
         <v/>
       </c>
       <c r="J14" s="19">
-        <f>SUM(J10:J13)</f>
+        <f>J8-J13</f>
         <v/>
       </c>
       <c r="K14" s="19">
-        <f>SUM(K10:K13)</f>
+        <f>K8-K13</f>
         <v/>
       </c>
       <c r="L14" s="19">
-        <f>SUM(L10:L13)</f>
+        <f>L8-L13</f>
         <v/>
       </c>
       <c r="M14" s="19">
-        <f>SUM(M10:M13)</f>
+        <f>M8-M13</f>
         <v/>
       </c>
       <c r="N14" s="19">
-        <f>SUM(N10:N13)</f>
+        <f>N8-N13</f>
         <v/>
       </c>
       <c r="O14" s="19">
-        <f>SUM(O10:O13)</f>
+        <f>O8-O13</f>
         <v/>
       </c>
       <c r="P14" s="19">
-        <f>SUM(P10:P13)</f>
+        <f>P8-P13</f>
         <v/>
       </c>
       <c r="Q14" s="19">
-        <f>SUM(Q10:Q13)</f>
+        <f>Q8-Q13</f>
         <v/>
       </c>
       <c r="R14" s="19">
-        <f>SUM(R10:R13)</f>
+        <f>R8-R13</f>
         <v/>
       </c>
       <c r="S14" s="19">
-        <f>SUM(S10:S13)</f>
+        <f>S8-S13</f>
         <v/>
       </c>
       <c r="T14" s="20">
@@ -3120,81 +4497,81 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Operating Income / (Loss)</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Interest (parent note)</t>
         </is>
       </c>
       <c r="B15" s="19">
-        <f>B8-B14</f>
+        <f>'Cash &amp; Note'!B6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="C15" s="19">
-        <f>C8-C14</f>
+        <f>'Cash &amp; Note'!C6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="D15" s="19">
-        <f>D8-D14</f>
+        <f>'Cash &amp; Note'!D6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="E15" s="19">
-        <f>E8-E14</f>
+        <f>'Cash &amp; Note'!E6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="F15" s="19">
-        <f>F8-F14</f>
+        <f>'Cash &amp; Note'!F6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="G15" s="19">
-        <f>G8-G14</f>
+        <f>'Cash &amp; Note'!G6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="H15" s="19">
-        <f>H8-H14</f>
+        <f>'Cash &amp; Note'!H6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="I15" s="19">
-        <f>I8-I14</f>
+        <f>'Cash &amp; Note'!I6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="J15" s="19">
-        <f>J8-J14</f>
+        <f>'Cash &amp; Note'!J6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="K15" s="19">
-        <f>K8-K14</f>
+        <f>'Cash &amp; Note'!K6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="L15" s="19">
-        <f>L8-L14</f>
+        <f>'Cash &amp; Note'!L6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="M15" s="19">
-        <f>M8-M14</f>
+        <f>'Cash &amp; Note'!M6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="N15" s="19">
-        <f>N8-N14</f>
+        <f>'Cash &amp; Note'!N6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="O15" s="19">
-        <f>O8-O14</f>
+        <f>'Cash &amp; Note'!O6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="P15" s="19">
-        <f>P8-P14</f>
+        <f>'Cash &amp; Note'!P6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="Q15" s="19">
-        <f>Q8-Q14</f>
+        <f>'Cash &amp; Note'!Q6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="R15" s="19">
-        <f>R8-R14</f>
+        <f>'Cash &amp; Note'!R6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="S15" s="19">
-        <f>S8-S14</f>
+        <f>'Cash &amp; Note'!S6*Drivers!$B$17/12</f>
         <v/>
       </c>
       <c r="T15" s="20">
@@ -3207,81 +4584,81 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Interest (parent note)</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Net Income / (Loss)</t>
         </is>
       </c>
       <c r="B16" s="19">
-        <f>'Cash &amp; Note'!B6*Drivers!$B$18/12</f>
+        <f>B14-B15</f>
         <v/>
       </c>
       <c r="C16" s="19">
-        <f>'Cash &amp; Note'!C6*Drivers!$B$18/12</f>
+        <f>C14-C15</f>
         <v/>
       </c>
       <c r="D16" s="19">
-        <f>'Cash &amp; Note'!D6*Drivers!$B$18/12</f>
+        <f>D14-D15</f>
         <v/>
       </c>
       <c r="E16" s="19">
-        <f>'Cash &amp; Note'!E6*Drivers!$B$18/12</f>
+        <f>E14-E15</f>
         <v/>
       </c>
       <c r="F16" s="19">
-        <f>'Cash &amp; Note'!F6*Drivers!$B$18/12</f>
+        <f>F14-F15</f>
         <v/>
       </c>
       <c r="G16" s="19">
-        <f>'Cash &amp; Note'!G6*Drivers!$B$18/12</f>
+        <f>G14-G15</f>
         <v/>
       </c>
       <c r="H16" s="19">
-        <f>'Cash &amp; Note'!H6*Drivers!$B$18/12</f>
+        <f>H14-H15</f>
         <v/>
       </c>
       <c r="I16" s="19">
-        <f>'Cash &amp; Note'!I6*Drivers!$B$18/12</f>
+        <f>I14-I15</f>
         <v/>
       </c>
       <c r="J16" s="19">
-        <f>'Cash &amp; Note'!J6*Drivers!$B$18/12</f>
+        <f>J14-J15</f>
         <v/>
       </c>
       <c r="K16" s="19">
-        <f>'Cash &amp; Note'!K6*Drivers!$B$18/12</f>
+        <f>K14-K15</f>
         <v/>
       </c>
       <c r="L16" s="19">
-        <f>'Cash &amp; Note'!L6*Drivers!$B$18/12</f>
+        <f>L14-L15</f>
         <v/>
       </c>
       <c r="M16" s="19">
-        <f>'Cash &amp; Note'!M6*Drivers!$B$18/12</f>
+        <f>M14-M15</f>
         <v/>
       </c>
       <c r="N16" s="19">
-        <f>'Cash &amp; Note'!N6*Drivers!$B$18/12</f>
+        <f>N14-N15</f>
         <v/>
       </c>
       <c r="O16" s="19">
-        <f>'Cash &amp; Note'!O6*Drivers!$B$18/12</f>
+        <f>O14-O15</f>
         <v/>
       </c>
       <c r="P16" s="19">
-        <f>'Cash &amp; Note'!P6*Drivers!$B$18/12</f>
+        <f>P14-P15</f>
         <v/>
       </c>
       <c r="Q16" s="19">
-        <f>'Cash &amp; Note'!Q6*Drivers!$B$18/12</f>
+        <f>Q14-Q15</f>
         <v/>
       </c>
       <c r="R16" s="19">
-        <f>'Cash &amp; Note'!R6*Drivers!$B$18/12</f>
+        <f>R14-R15</f>
         <v/>
       </c>
       <c r="S16" s="19">
-        <f>'Cash &amp; Note'!S6*Drivers!$B$18/12</f>
+        <f>S14-S15</f>
         <v/>
       </c>
       <c r="T16" s="20">
@@ -3294,183 +4671,103 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Net Income / (Loss)</t>
-        </is>
-      </c>
-      <c r="B17" s="19">
-        <f>B15-B16</f>
-        <v/>
-      </c>
-      <c r="C17" s="19">
-        <f>C15-C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="19">
-        <f>D15-D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="19">
-        <f>E15-E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="19">
-        <f>F15-F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="19">
-        <f>G15-G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="19">
-        <f>H15-H16</f>
-        <v/>
-      </c>
-      <c r="I17" s="19">
-        <f>I15-I16</f>
-        <v/>
-      </c>
-      <c r="J17" s="19">
-        <f>J15-J16</f>
-        <v/>
-      </c>
-      <c r="K17" s="19">
-        <f>K15-K16</f>
-        <v/>
-      </c>
-      <c r="L17" s="19">
-        <f>L15-L16</f>
-        <v/>
-      </c>
-      <c r="M17" s="19">
-        <f>M15-M16</f>
-        <v/>
-      </c>
-      <c r="N17" s="19">
-        <f>N15-N16</f>
-        <v/>
-      </c>
-      <c r="O17" s="19">
-        <f>O15-O16</f>
-        <v/>
-      </c>
-      <c r="P17" s="19">
-        <f>P15-P16</f>
-        <v/>
-      </c>
-      <c r="Q17" s="19">
-        <f>Q15-Q16</f>
-        <v/>
-      </c>
-      <c r="R17" s="19">
-        <f>R15-R16</f>
-        <v/>
-      </c>
-      <c r="S17" s="19">
-        <f>S15-S16</f>
-        <v/>
-      </c>
-      <c r="T17" s="20">
-        <f>SUM(B17:G17)</f>
-        <v/>
-      </c>
-      <c r="U17" s="20">
-        <f>SUM(H17:S17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>OILI return % (OI − interest) ÷ revenue</t>
         </is>
       </c>
-      <c r="B18" s="21">
-        <f>(B15-B16)/B6</f>
-        <v/>
-      </c>
-      <c r="C18" s="21">
-        <f>(C15-C16)/C6</f>
-        <v/>
-      </c>
-      <c r="D18" s="21">
-        <f>(D15-D16)/D6</f>
-        <v/>
-      </c>
-      <c r="E18" s="21">
-        <f>(E15-E16)/E6</f>
-        <v/>
-      </c>
-      <c r="F18" s="21">
-        <f>(F15-F16)/F6</f>
-        <v/>
-      </c>
-      <c r="G18" s="21">
-        <f>(G15-G16)/G6</f>
-        <v/>
-      </c>
-      <c r="H18" s="21">
-        <f>(H15-H16)/H6</f>
-        <v/>
-      </c>
-      <c r="I18" s="21">
-        <f>(I15-I16)/I6</f>
-        <v/>
-      </c>
-      <c r="J18" s="21">
-        <f>(J15-J16)/J6</f>
-        <v/>
-      </c>
-      <c r="K18" s="21">
-        <f>(K15-K16)/K6</f>
-        <v/>
-      </c>
-      <c r="L18" s="21">
-        <f>(L15-L16)/L6</f>
-        <v/>
-      </c>
-      <c r="M18" s="21">
-        <f>(M15-M16)/M6</f>
-        <v/>
-      </c>
-      <c r="N18" s="21">
-        <f>(N15-N16)/N6</f>
-        <v/>
-      </c>
-      <c r="O18" s="21">
-        <f>(O15-O16)/O6</f>
-        <v/>
-      </c>
-      <c r="P18" s="21">
-        <f>(P15-P16)/P6</f>
-        <v/>
-      </c>
-      <c r="Q18" s="21">
-        <f>(Q15-Q16)/Q6</f>
-        <v/>
-      </c>
-      <c r="R18" s="21">
-        <f>(R15-R16)/R6</f>
-        <v/>
-      </c>
-      <c r="S18" s="21">
-        <f>(S15-S16)/S6</f>
-        <v/>
-      </c>
-      <c r="T18" s="21">
-        <f>(T15-T16)/T6</f>
-        <v/>
-      </c>
-      <c r="U18" s="21">
-        <f>(U15-U16)/U6</f>
-        <v/>
+      <c r="B17" s="21">
+        <f>(B14-B15)/B6</f>
+        <v/>
+      </c>
+      <c r="C17" s="21">
+        <f>(C14-C15)/C6</f>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>(D14-D15)/D6</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>(E14-E15)/E6</f>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>(F14-F15)/F6</f>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>(G14-G15)/G6</f>
+        <v/>
+      </c>
+      <c r="H17" s="21">
+        <f>(H14-H15)/H6</f>
+        <v/>
+      </c>
+      <c r="I17" s="21">
+        <f>(I14-I15)/I6</f>
+        <v/>
+      </c>
+      <c r="J17" s="21">
+        <f>(J14-J15)/J6</f>
+        <v/>
+      </c>
+      <c r="K17" s="21">
+        <f>(K14-K15)/K6</f>
+        <v/>
+      </c>
+      <c r="L17" s="21">
+        <f>(L14-L15)/L6</f>
+        <v/>
+      </c>
+      <c r="M17" s="21">
+        <f>(M14-M15)/M6</f>
+        <v/>
+      </c>
+      <c r="N17" s="21">
+        <f>(N14-N15)/N6</f>
+        <v/>
+      </c>
+      <c r="O17" s="21">
+        <f>(O14-O15)/O6</f>
+        <v/>
+      </c>
+      <c r="P17" s="21">
+        <f>(P14-P15)/P6</f>
+        <v/>
+      </c>
+      <c r="Q17" s="21">
+        <f>(Q14-Q15)/Q6</f>
+        <v/>
+      </c>
+      <c r="R17" s="21">
+        <f>(R14-R15)/R6</f>
+        <v/>
+      </c>
+      <c r="S17" s="21">
+        <f>(S14-S15)/S6</f>
+        <v/>
+      </c>
+      <c r="T17" s="21">
+        <f>(T14-T15)/T6</f>
+        <v/>
+      </c>
+      <c r="U17" s="21">
+        <f>(U14-U15)/U6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Cost structure reconciled to the 2026 CVR Budget (finance): direct labor = billable hours × $54.89; total labor is fixed per FTE, so utilization gains flow to Operating Income. At the budget operating point (9.72 FTE, 70% util, ~$142.85 realized) this reproduces the budget's $104.1K GP and $11.6K OI/month.</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Direct labor follows the GL convention (~92% of wages charged to jobs), so gross margin here is comparable to the GL statements — improvement comes from revenue per FTE, not reclassification.</t>
+          <t>BUDGET (finance, flat monthly): Revenue $169.1K · Direct labor $65.0K · GP $104.1K · OpEx $92.5K · Operating Income $11.6K · Interest $0 · Net Income $11.6K. Full monthly compare on the 'vs Budget' tab.</t>
         </is>
       </c>
     </row>
@@ -3480,6 +4777,446 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast vs 2026 Budget (finance) — H2-2026, line by line ($K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Budget = flat monthly per the 2026 CVR Budget V5. Forecast = active scenario from Forecast P&amp;L. Δ = Forecast − Budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>H2-2026 ($K)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Δ (Fcst − Bud)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Δ %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B5" s="19">
+        <f>SUM('Forecast P&amp;L'!B6:G6)</f>
+        <v/>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>1014.6</v>
+      </c>
+      <c r="D5" s="19">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="10">
+        <f>IF(C5=0,"n/a",B5/C5-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Direct labor</t>
+        </is>
+      </c>
+      <c r="B6" s="19">
+        <f>SUM('Forecast P&amp;L'!B7:G7)</f>
+        <v/>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>389.9</v>
+      </c>
+      <c r="D6" s="19">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="10">
+        <f>IF(C6=0,"n/a",B6/C6-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B7" s="23">
+        <f>SUM('Forecast P&amp;L'!B8:G8)</f>
+        <v/>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>624.7</v>
+      </c>
+      <c r="D7" s="23">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="10">
+        <f>IF(C7=0,"n/a",B7/C7-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B8" s="19">
+        <f>SUM('Forecast P&amp;L'!B13:G13)</f>
+        <v/>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>555</v>
+      </c>
+      <c r="D8" s="19">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="10">
+        <f>IF(C8=0,"n/a",B8/C8-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B9" s="23">
+        <f>SUM('Forecast P&amp;L'!B14:G14)</f>
+        <v/>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="D9" s="23">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="10">
+        <f>IF(C9=0,"n/a",B9/C9-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>SUM('Forecast P&amp;L'!B15:G15)</f>
+        <v/>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(C10=0,"n/a",B10/C10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B11" s="23">
+        <f>SUM('Forecast P&amp;L'!B16:G16)</f>
+        <v/>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="D11" s="23">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="10">
+        <f>IF(C11=0,"n/a",B11/C11-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Full monthly budget (flat) for reference:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Budget $K</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Oct-26</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Nov-26</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Dec-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>169.1</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>169.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Direct labor</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>104.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Budget carries $0 interest; the forecast accrues ~$5K/mo on the parent note — so forecast Net Income trails</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>budget by roughly that amount even at matched operating performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>The full-year budget ($2,029K revenue / +$139K NI) is a flat 1/12 spread; H1 landed 46% under it, so the</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>meaningful compare is H2 forward — shown above — plus the FY landing on the FY Summary tab.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3627,75 +5364,75 @@
         </is>
       </c>
       <c r="B5" s="19">
-        <f>'Forecast P&amp;L'!B17</f>
+        <f>'Forecast P&amp;L'!B16</f>
         <v/>
       </c>
       <c r="C5" s="19">
-        <f>'Forecast P&amp;L'!C17</f>
+        <f>'Forecast P&amp;L'!C16</f>
         <v/>
       </c>
       <c r="D5" s="19">
-        <f>'Forecast P&amp;L'!D17</f>
+        <f>'Forecast P&amp;L'!D16</f>
         <v/>
       </c>
       <c r="E5" s="19">
-        <f>'Forecast P&amp;L'!E17</f>
+        <f>'Forecast P&amp;L'!E16</f>
         <v/>
       </c>
       <c r="F5" s="19">
-        <f>'Forecast P&amp;L'!F17</f>
+        <f>'Forecast P&amp;L'!F16</f>
         <v/>
       </c>
       <c r="G5" s="19">
-        <f>'Forecast P&amp;L'!G17</f>
+        <f>'Forecast P&amp;L'!G16</f>
         <v/>
       </c>
       <c r="H5" s="19">
-        <f>'Forecast P&amp;L'!H17</f>
+        <f>'Forecast P&amp;L'!H16</f>
         <v/>
       </c>
       <c r="I5" s="19">
-        <f>'Forecast P&amp;L'!I17</f>
+        <f>'Forecast P&amp;L'!I16</f>
         <v/>
       </c>
       <c r="J5" s="19">
-        <f>'Forecast P&amp;L'!J17</f>
+        <f>'Forecast P&amp;L'!J16</f>
         <v/>
       </c>
       <c r="K5" s="19">
-        <f>'Forecast P&amp;L'!K17</f>
+        <f>'Forecast P&amp;L'!K16</f>
         <v/>
       </c>
       <c r="L5" s="19">
-        <f>'Forecast P&amp;L'!L17</f>
+        <f>'Forecast P&amp;L'!L16</f>
         <v/>
       </c>
       <c r="M5" s="19">
-        <f>'Forecast P&amp;L'!M17</f>
+        <f>'Forecast P&amp;L'!M16</f>
         <v/>
       </c>
       <c r="N5" s="19">
-        <f>'Forecast P&amp;L'!N17</f>
+        <f>'Forecast P&amp;L'!N16</f>
         <v/>
       </c>
       <c r="O5" s="19">
-        <f>'Forecast P&amp;L'!O17</f>
+        <f>'Forecast P&amp;L'!O16</f>
         <v/>
       </c>
       <c r="P5" s="19">
-        <f>'Forecast P&amp;L'!P17</f>
+        <f>'Forecast P&amp;L'!P16</f>
         <v/>
       </c>
       <c r="Q5" s="19">
-        <f>'Forecast P&amp;L'!Q17</f>
+        <f>'Forecast P&amp;L'!Q16</f>
         <v/>
       </c>
       <c r="R5" s="19">
-        <f>'Forecast P&amp;L'!R17</f>
+        <f>'Forecast P&amp;L'!R16</f>
         <v/>
       </c>
       <c r="S5" s="19">
-        <f>'Forecast P&amp;L'!S17</f>
+        <f>'Forecast P&amp;L'!S16</f>
         <v/>
       </c>
     </row>
@@ -3784,75 +5521,75 @@
         </is>
       </c>
       <c r="B7" s="19">
-        <f>'Forecast P&amp;L'!B6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!B6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>'Forecast P&amp;L'!C6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!C6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="D7" s="19">
-        <f>'Forecast P&amp;L'!D6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!D6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="E7" s="19">
-        <f>'Forecast P&amp;L'!E6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!E6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="F7" s="19">
-        <f>'Forecast P&amp;L'!F6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!F6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="G7" s="19">
-        <f>'Forecast P&amp;L'!G6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!G6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="H7" s="19">
-        <f>'Forecast P&amp;L'!H6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!H6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="I7" s="19">
-        <f>'Forecast P&amp;L'!I6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!I6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="J7" s="19">
-        <f>'Forecast P&amp;L'!J6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!J6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="K7" s="19">
-        <f>'Forecast P&amp;L'!K6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!K6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="L7" s="19">
-        <f>'Forecast P&amp;L'!L6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!L6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="M7" s="19">
-        <f>'Forecast P&amp;L'!M6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!M6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="N7" s="19">
-        <f>'Forecast P&amp;L'!N6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!N6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="O7" s="19">
-        <f>'Forecast P&amp;L'!O6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!O6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="P7" s="19">
-        <f>'Forecast P&amp;L'!P6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!P6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="Q7" s="19">
-        <f>'Forecast P&amp;L'!Q6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!Q6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="R7" s="19">
-        <f>'Forecast P&amp;L'!R6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!R6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
       <c r="S7" s="19">
-        <f>'Forecast P&amp;L'!S6*Drivers!$B$19/30.4</f>
+        <f>'Forecast P&amp;L'!S6*Drivers!$B$18/30.4</f>
         <v/>
       </c>
     </row>
@@ -4105,7 +5842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4468,7 +6205,7 @@
           <t>Total backlog remaining</t>
         </is>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="24">
         <f>SUM(E5:E13)</f>
         <v/>
       </c>
@@ -4680,7 +6417,7 @@
           <t>Total probability-weighted pipeline</t>
         </is>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="24">
         <f>SUM(E18:E23)</f>
         <v/>
       </c>
@@ -4737,7 +6474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4860,7 +6597,7 @@
         <v>-290.5</v>
       </c>
       <c r="C7" s="19">
-        <f>'Forecast P&amp;L'!T15</f>
+        <f>'Forecast P&amp;L'!T14</f>
         <v/>
       </c>
       <c r="D7" s="23">
@@ -4885,7 +6622,7 @@
         <v>30.1</v>
       </c>
       <c r="C8" s="19">
-        <f>'Forecast P&amp;L'!T16</f>
+        <f>'Forecast P&amp;L'!T15</f>
         <v/>
       </c>
       <c r="D8" s="23">
@@ -4910,7 +6647,7 @@
         <v>-320.5</v>
       </c>
       <c r="C9" s="19">
-        <f>'Forecast P&amp;L'!T17</f>
+        <f>'Forecast P&amp;L'!T16</f>
         <v/>
       </c>
       <c r="D9" s="23">
@@ -4942,7 +6679,7 @@
           <t>Note balance at 12/31/26</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <f>'Cash &amp; Note'!G10</f>
         <v/>
       </c>
@@ -5005,7 +6742,7 @@
         </is>
       </c>
       <c r="B16" s="19">
-        <f>'Forecast P&amp;L'!U15</f>
+        <f>'Forecast P&amp;L'!U14</f>
         <v/>
       </c>
     </row>
@@ -5016,7 +6753,7 @@
         </is>
       </c>
       <c r="B17" s="19">
-        <f>'Forecast P&amp;L'!U17</f>
+        <f>'Forecast P&amp;L'!U16</f>
         <v/>
       </c>
     </row>
@@ -5027,7 +6764,7 @@
         </is>
       </c>
       <c r="B18" s="21">
-        <f>('Forecast P&amp;L'!U15-'Forecast P&amp;L'!U16)/'Forecast P&amp;L'!U6</f>
+        <f>('Forecast P&amp;L'!U14-'Forecast P&amp;L'!U15)/'Forecast P&amp;L'!U6</f>
         <v/>
       </c>
     </row>
@@ -5037,7 +6774,7 @@
           <t>Note balance at 12/31/27</t>
         </is>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="25">
         <f>'Cash &amp; Note'!S10</f>
         <v/>
       </c>
@@ -5054,7 +6791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5236,1387 +6973,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Forecast &amp; work coverage — with pipeline toggle</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Native chart wired to live cells. Set the toggle to 0 to see booked backlog only; edit job remainders or bid probabilities and everything redraws.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Include weighted pipeline? (1 = yes, 0 = no)</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Coverage of forecast</t>
-        </is>
-      </c>
-      <c r="B5" s="25">
-        <f>(SUM(B34:S34)+SUM(B40:S40))/SUM(B41:S41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Gap to originate ($K)</t>
-        </is>
-      </c>
-      <c r="B6" s="26">
-        <f>SUM(B41:S41)-SUM(B34:S34)-SUM(B40:S40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>CHART DATA ($K/month) — formulas reference Backlog &amp; Pipeline and Forecast P&amp;L</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Aug-26</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Sep-26</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Oct-26</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Nov-26</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Dec-26</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Jan-27</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Feb-27</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Mar-27</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Apr-27</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>May-27</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Jun-27</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Jul-27</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Aug-27</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Sep-27</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Oct-27</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Nov-27</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Dec-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>burn: DTE — Catalina Conversion Ph 3</t>
-        </is>
-      </c>
-      <c r="B25">
-        <f>'Backlog &amp; Pipeline'!$E5/6</f>
-        <v/>
-      </c>
-      <c r="C25">
-        <f>'Backlog &amp; Pipeline'!$E5/6</f>
-        <v/>
-      </c>
-      <c r="D25">
-        <f>'Backlog &amp; Pipeline'!$E5/6</f>
-        <v/>
-      </c>
-      <c r="E25">
-        <f>'Backlog &amp; Pipeline'!$E5/6</f>
-        <v/>
-      </c>
-      <c r="F25">
-        <f>'Backlog &amp; Pipeline'!$E5/6</f>
-        <v/>
-      </c>
-      <c r="G25">
-        <f>'Backlog &amp; Pipeline'!$E5/6</f>
-        <v/>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>burn: DTE — New Baltimore Conversion</t>
-        </is>
-      </c>
-      <c r="B26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="C26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="D26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="E26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="F26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="G26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="H26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="I26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="J26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="K26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="L26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="M26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="N26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="O26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="P26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="Q26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="R26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-      <c r="S26">
-        <f>'Backlog &amp; Pipeline'!$E6/18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>burn: Consumers — 2026 HVD Line Sensors</t>
-        </is>
-      </c>
-      <c r="B27">
-        <f>'Backlog &amp; Pipeline'!$E7/4</f>
-        <v/>
-      </c>
-      <c r="C27">
-        <f>'Backlog &amp; Pipeline'!$E7/4</f>
-        <v/>
-      </c>
-      <c r="D27">
-        <f>'Backlog &amp; Pipeline'!$E7/4</f>
-        <v/>
-      </c>
-      <c r="E27">
-        <f>'Backlog &amp; Pipeline'!$E7/4</f>
-        <v/>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>burn: Cloverland — Manistique Pump Stn</t>
-        </is>
-      </c>
-      <c r="B28">
-        <f>'Backlog &amp; Pipeline'!$E8/3</f>
-        <v/>
-      </c>
-      <c r="C28">
-        <f>'Backlog &amp; Pipeline'!$E8/3</f>
-        <v/>
-      </c>
-      <c r="D28">
-        <f>'Backlog &amp; Pipeline'!$E8/3</f>
-        <v/>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>burn: CenterPoint — Gateway 69kV</t>
-        </is>
-      </c>
-      <c r="B29">
-        <f>'Backlog &amp; Pipeline'!$E9/2</f>
-        <v/>
-      </c>
-      <c r="C29">
-        <f>'Backlog &amp; Pipeline'!$E9/2</f>
-        <v/>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>burn: CenterPoint — Rockport 69kV</t>
-        </is>
-      </c>
-      <c r="B30">
-        <f>'Backlog &amp; Pipeline'!$E10/2</f>
-        <v/>
-      </c>
-      <c r="C30">
-        <f>'Backlog &amp; Pipeline'!$E10/2</f>
-        <v/>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>burn: CenterPoint — Angel Mounds 69kV</t>
-        </is>
-      </c>
-      <c r="B31">
-        <f>'Backlog &amp; Pipeline'!$E11/4</f>
-        <v/>
-      </c>
-      <c r="C31">
-        <f>'Backlog &amp; Pipeline'!$E11/4</f>
-        <v/>
-      </c>
-      <c r="D31">
-        <f>'Backlog &amp; Pipeline'!$E11/4</f>
-        <v/>
-      </c>
-      <c r="E31">
-        <f>'Backlog &amp; Pipeline'!$E11/4</f>
-        <v/>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>burn: CenterPoint — Northwest 69kV</t>
-        </is>
-      </c>
-      <c r="B32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="C32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="D32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="E32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="F32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="G32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="H32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="I32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="J32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="K32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="L32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="M32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="N32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="O32">
-        <f>'Backlog &amp; Pipeline'!$E12/14</f>
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>burn: CenterPoint — Leonard Rd 69kV</t>
-        </is>
-      </c>
-      <c r="B33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="C33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="D33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="E33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="F33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="G33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="H33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="I33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="J33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="K33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="L33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="M33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="N33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="O33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="P33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="Q33">
-        <f>'Backlog &amp; Pipeline'!$E13/16</f>
-        <v/>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Booked backlog</t>
-        </is>
-      </c>
-      <c r="B34">
-        <f>SUM(B25:B33)</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>SUM(C25:C33)</f>
-        <v/>
-      </c>
-      <c r="D34">
-        <f>SUM(D25:D33)</f>
-        <v/>
-      </c>
-      <c r="E34">
-        <f>SUM(E25:E33)</f>
-        <v/>
-      </c>
-      <c r="F34">
-        <f>SUM(F25:F33)</f>
-        <v/>
-      </c>
-      <c r="G34">
-        <f>SUM(G25:G33)</f>
-        <v/>
-      </c>
-      <c r="H34">
-        <f>SUM(H25:H33)</f>
-        <v/>
-      </c>
-      <c r="I34">
-        <f>SUM(I25:I33)</f>
-        <v/>
-      </c>
-      <c r="J34">
-        <f>SUM(J25:J33)</f>
-        <v/>
-      </c>
-      <c r="K34">
-        <f>SUM(K25:K33)</f>
-        <v/>
-      </c>
-      <c r="L34">
-        <f>SUM(L25:L33)</f>
-        <v/>
-      </c>
-      <c r="M34">
-        <f>SUM(M25:M33)</f>
-        <v/>
-      </c>
-      <c r="N34">
-        <f>SUM(N25:N33)</f>
-        <v/>
-      </c>
-      <c r="O34">
-        <f>SUM(O25:O33)</f>
-        <v/>
-      </c>
-      <c r="P34">
-        <f>SUM(P25:P33)</f>
-        <v/>
-      </c>
-      <c r="Q34">
-        <f>SUM(Q25:Q33)</f>
-        <v/>
-      </c>
-      <c r="R34">
-        <f>SUM(R25:R33)</f>
-        <v/>
-      </c>
-      <c r="S34">
-        <f>SUM(S25:S33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>bid: Frontier Make Ready</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
-        <v/>
-      </c>
-      <c r="E35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
-        <v/>
-      </c>
-      <c r="F35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
-        <v/>
-      </c>
-      <c r="G35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
-        <v/>
-      </c>
-      <c r="H35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
-        <v/>
-      </c>
-      <c r="I35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
-        <v/>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>bid: Jacksonburg–Gateway (EPC-paired $3</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="G36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="H36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="I36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="J36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="K36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="L36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="M36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="N36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="O36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="P36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="Q36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>bid: Rosehill–Rockport (EPC-paired $5.5</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="G37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="H37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="I37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="J37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="K37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="L37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="M37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="N37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="O37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="P37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="Q37">
-        <f>'Backlog &amp; Pipeline'!$C20*'Backlog &amp; Pipeline'!$D20/12</f>
-        <v/>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>bid: Joint Use Audit</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="H38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="I38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="J38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="K38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="L38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="M38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="N38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="O38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="P38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="Q38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="R38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="S38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>bid: 2026 Pole Replacements (EPC-paired</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="G39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="H39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="I39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="J39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="K39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="L39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="M39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="N39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="O39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="P39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="Q39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Weighted pipeline (× toggle)</t>
-        </is>
-      </c>
-      <c r="B40">
-        <f>SUM(B35:B39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="C40">
-        <f>SUM(C35:C39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="D40">
-        <f>SUM(D35:D39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="E40">
-        <f>SUM(E35:E39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="F40">
-        <f>SUM(F35:F39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="G40">
-        <f>SUM(G35:G39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="H40">
-        <f>SUM(H35:H39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="I40">
-        <f>SUM(I35:I39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="J40">
-        <f>SUM(J35:J39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="K40">
-        <f>SUM(K35:K39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="L40">
-        <f>SUM(L35:L39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="M40">
-        <f>SUM(M35:M39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="N40">
-        <f>SUM(N35:N39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="O40">
-        <f>SUM(O35:O39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="P40">
-        <f>SUM(P35:P39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="Q40">
-        <f>SUM(Q35:Q39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="R40">
-        <f>SUM(R35:R39)*$B$3</f>
-        <v/>
-      </c>
-      <c r="S40">
-        <f>SUM(S35:S39)*$B$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Forecast revenue</t>
-        </is>
-      </c>
-      <c r="B41">
-        <f>'Forecast P&amp;L'!B6</f>
-        <v/>
-      </c>
-      <c r="C41">
-        <f>'Forecast P&amp;L'!C6</f>
-        <v/>
-      </c>
-      <c r="D41">
-        <f>'Forecast P&amp;L'!D6</f>
-        <v/>
-      </c>
-      <c r="E41">
-        <f>'Forecast P&amp;L'!E6</f>
-        <v/>
-      </c>
-      <c r="F41">
-        <f>'Forecast P&amp;L'!F6</f>
-        <v/>
-      </c>
-      <c r="G41">
-        <f>'Forecast P&amp;L'!G6</f>
-        <v/>
-      </c>
-      <c r="H41">
-        <f>'Forecast P&amp;L'!H6</f>
-        <v/>
-      </c>
-      <c r="I41">
-        <f>'Forecast P&amp;L'!I6</f>
-        <v/>
-      </c>
-      <c r="J41">
-        <f>'Forecast P&amp;L'!J6</f>
-        <v/>
-      </c>
-      <c r="K41">
-        <f>'Forecast P&amp;L'!K6</f>
-        <v/>
-      </c>
-      <c r="L41">
-        <f>'Forecast P&amp;L'!L6</f>
-        <v/>
-      </c>
-      <c r="M41">
-        <f>'Forecast P&amp;L'!M6</f>
-        <v/>
-      </c>
-      <c r="N41">
-        <f>'Forecast P&amp;L'!N6</f>
-        <v/>
-      </c>
-      <c r="O41">
-        <f>'Forecast P&amp;L'!O6</f>
-        <v/>
-      </c>
-      <c r="P41">
-        <f>'Forecast P&amp;L'!P6</f>
-        <v/>
-      </c>
-      <c r="Q41">
-        <f>'Forecast P&amp;L'!Q6</f>
-        <v/>
-      </c>
-      <c r="R41">
-        <f>'Forecast P&amp;L'!R6</f>
-        <v/>
-      </c>
-      <c r="S41">
-        <f>'Forecast P&amp;L'!S6</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/model/CVR_Model_Phase2_Forecast.xlsx
+++ b/model/CVR_Model_Phase2_Forecast.xlsx
@@ -239,7 +239,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Coverage Chart'!A34</f>
+              <f>'Coverage Chart'!A35</f>
             </strRef>
           </tx>
           <spPr>
@@ -257,7 +257,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Coverage Chart'!$B$34:$S$34</f>
+              <f>'Coverage Chart'!$B$35:$S$35</f>
             </numRef>
           </val>
         </ser>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B5" s="26">
-        <f>(SUM(B34:S34)+SUM(B40:S40))/SUM(B41:S41)</f>
+        <f>(SUM(B35:S35)+SUM(B40:S40))/SUM(B41:S41)</f>
         <v/>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>SUM(B41:S41)-SUM(B34:S34)-SUM(B40:S40)</f>
+        <f>SUM(B41:S41)-SUM(B35:S35)-SUM(B40:S40)</f>
         <v/>
       </c>
     </row>
@@ -1676,155 +1676,167 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>burn: Consumers — 2026 Pole Replacements</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="J34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="M34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="O34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="P34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="Q34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="R34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+      <c r="S34">
+        <f>'Backlog &amp; Pipeline'!$E14/18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Booked backlog</t>
         </is>
       </c>
-      <c r="B34">
-        <f>SUM(B25:B33)</f>
-        <v/>
-      </c>
-      <c r="C34">
-        <f>SUM(C25:C33)</f>
-        <v/>
-      </c>
-      <c r="D34">
-        <f>SUM(D25:D33)</f>
-        <v/>
-      </c>
-      <c r="E34">
-        <f>SUM(E25:E33)</f>
-        <v/>
-      </c>
-      <c r="F34">
-        <f>SUM(F25:F33)</f>
-        <v/>
-      </c>
-      <c r="G34">
-        <f>SUM(G25:G33)</f>
-        <v/>
-      </c>
-      <c r="H34">
-        <f>SUM(H25:H33)</f>
-        <v/>
-      </c>
-      <c r="I34">
-        <f>SUM(I25:I33)</f>
-        <v/>
-      </c>
-      <c r="J34">
-        <f>SUM(J25:J33)</f>
-        <v/>
-      </c>
-      <c r="K34">
-        <f>SUM(K25:K33)</f>
-        <v/>
-      </c>
-      <c r="L34">
-        <f>SUM(L25:L33)</f>
-        <v/>
-      </c>
-      <c r="M34">
-        <f>SUM(M25:M33)</f>
-        <v/>
-      </c>
-      <c r="N34">
-        <f>SUM(N25:N33)</f>
-        <v/>
-      </c>
-      <c r="O34">
-        <f>SUM(O25:O33)</f>
-        <v/>
-      </c>
-      <c r="P34">
-        <f>SUM(P25:P33)</f>
-        <v/>
-      </c>
-      <c r="Q34">
-        <f>SUM(Q25:Q33)</f>
-        <v/>
-      </c>
-      <c r="R34">
-        <f>SUM(R25:R33)</f>
-        <v/>
-      </c>
-      <c r="S34">
-        <f>SUM(S25:S33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>bid: Frontier Make Ready</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
+      <c r="B35">
+        <f>SUM(B25:B34)</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>SUM(C25:C34)</f>
+        <v/>
       </c>
       <c r="D35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <f>SUM(D25:D34)</f>
         <v/>
       </c>
       <c r="E35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <f>SUM(E25:E34)</f>
         <v/>
       </c>
       <c r="F35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <f>SUM(F25:F34)</f>
         <v/>
       </c>
       <c r="G35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <f>SUM(G25:G34)</f>
         <v/>
       </c>
       <c r="H35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
+        <f>SUM(H25:H34)</f>
         <v/>
       </c>
       <c r="I35">
-        <f>'Backlog &amp; Pipeline'!$C18*'Backlog &amp; Pipeline'!$D18/6</f>
-        <v/>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
+        <f>SUM(I25:I34)</f>
+        <v/>
+      </c>
+      <c r="J35">
+        <f>SUM(J25:J34)</f>
+        <v/>
+      </c>
+      <c r="K35">
+        <f>SUM(K25:K34)</f>
+        <v/>
+      </c>
+      <c r="L35">
+        <f>SUM(L25:L34)</f>
+        <v/>
+      </c>
+      <c r="M35">
+        <f>SUM(M25:M34)</f>
+        <v/>
+      </c>
+      <c r="N35">
+        <f>SUM(N25:N34)</f>
+        <v/>
+      </c>
+      <c r="O35">
+        <f>SUM(O25:O34)</f>
+        <v/>
+      </c>
+      <c r="P35">
+        <f>SUM(P25:P34)</f>
+        <v/>
+      </c>
+      <c r="Q35">
+        <f>SUM(Q25:Q34)</f>
+        <v/>
+      </c>
+      <c r="R35">
+        <f>SUM(R25:R34)</f>
+        <v/>
+      </c>
+      <c r="S35">
+        <f>SUM(S25:S34)</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>bid: Jacksonburg–Gateway (EPC-paired $3</t>
+          <t>bid: Frontier Make Ready</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1833,59 +1845,53 @@
       <c r="C36" t="n">
         <v>0</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
+      <c r="D36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/6</f>
+        <v/>
+      </c>
+      <c r="E36">
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/6</f>
+        <v/>
       </c>
       <c r="F36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/6</f>
         <v/>
       </c>
       <c r="G36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/6</f>
         <v/>
       </c>
       <c r="H36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/6</f>
         <v/>
       </c>
       <c r="I36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="J36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="K36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="L36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="M36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="N36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="O36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="P36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
-      </c>
-      <c r="Q36">
-        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/12</f>
-        <v/>
+        <f>'Backlog &amp; Pipeline'!$C19*'Backlog &amp; Pipeline'!$D19/6</f>
+        <v/>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -1897,7 +1903,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>bid: Rosehill–Rockport (EPC-paired $5.5</t>
+          <t>bid: Jacksonburg–Gateway (EPC-paired $3</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1970,7 +1976,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>bid: Joint Use Audit</t>
+          <t>bid: Rosehill–Rockport (EPC-paired $5.5</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1985,66 +1991,65 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
+      <c r="F38">
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
+        <v/>
       </c>
       <c r="G38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="H38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="I38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="J38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="K38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="L38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="M38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="N38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="O38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="P38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="R38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
-      </c>
-      <c r="S38">
-        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/18</f>
-        <v/>
+        <f>'Backlog &amp; Pipeline'!$C21*'Backlog &amp; Pipeline'!$D21/12</f>
+        <v/>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>bid: 2026 Pole Replacements (EPC-paired</t>
+          <t>bid: Joint Use Audit</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2059,59 +2064,60 @@
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
+      <c r="F39" t="n">
+        <v>0</v>
       </c>
       <c r="G39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="H39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="I39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="J39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="K39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="L39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="M39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="N39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="O39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="P39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/12</f>
-        <v/>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
+        <v/>
+      </c>
+      <c r="R39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
+        <v/>
+      </c>
+      <c r="S39">
+        <f>'Backlog &amp; Pipeline'!$C22*'Backlog &amp; Pipeline'!$D22/18</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2121,75 +2127,75 @@
         </is>
       </c>
       <c r="B40">
-        <f>SUM(B35:B39)*$B$3</f>
+        <f>SUM(B36:B39)*$B$3</f>
         <v/>
       </c>
       <c r="C40">
-        <f>SUM(C35:C39)*$B$3</f>
+        <f>SUM(C36:C39)*$B$3</f>
         <v/>
       </c>
       <c r="D40">
-        <f>SUM(D35:D39)*$B$3</f>
+        <f>SUM(D36:D39)*$B$3</f>
         <v/>
       </c>
       <c r="E40">
-        <f>SUM(E35:E39)*$B$3</f>
+        <f>SUM(E36:E39)*$B$3</f>
         <v/>
       </c>
       <c r="F40">
-        <f>SUM(F35:F39)*$B$3</f>
+        <f>SUM(F36:F39)*$B$3</f>
         <v/>
       </c>
       <c r="G40">
-        <f>SUM(G35:G39)*$B$3</f>
+        <f>SUM(G36:G39)*$B$3</f>
         <v/>
       </c>
       <c r="H40">
-        <f>SUM(H35:H39)*$B$3</f>
+        <f>SUM(H36:H39)*$B$3</f>
         <v/>
       </c>
       <c r="I40">
-        <f>SUM(I35:I39)*$B$3</f>
+        <f>SUM(I36:I39)*$B$3</f>
         <v/>
       </c>
       <c r="J40">
-        <f>SUM(J35:J39)*$B$3</f>
+        <f>SUM(J36:J39)*$B$3</f>
         <v/>
       </c>
       <c r="K40">
-        <f>SUM(K35:K39)*$B$3</f>
+        <f>SUM(K36:K39)*$B$3</f>
         <v/>
       </c>
       <c r="L40">
-        <f>SUM(L35:L39)*$B$3</f>
+        <f>SUM(L36:L39)*$B$3</f>
         <v/>
       </c>
       <c r="M40">
-        <f>SUM(M35:M39)*$B$3</f>
+        <f>SUM(M36:M39)*$B$3</f>
         <v/>
       </c>
       <c r="N40">
-        <f>SUM(N35:N39)*$B$3</f>
+        <f>SUM(N36:N39)*$B$3</f>
         <v/>
       </c>
       <c r="O40">
-        <f>SUM(O35:O39)*$B$3</f>
+        <f>SUM(O36:O39)*$B$3</f>
         <v/>
       </c>
       <c r="P40">
-        <f>SUM(P35:P39)*$B$3</f>
+        <f>SUM(P36:P39)*$B$3</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>SUM(Q35:Q39)*$B$3</f>
+        <f>SUM(Q36:Q39)*$B$3</f>
         <v/>
       </c>
       <c r="R40">
-        <f>SUM(R35:R39)*$B$3</f>
+        <f>SUM(R36:R39)*$B$3</f>
         <v/>
       </c>
       <c r="S40">
-        <f>SUM(S35:S39)*$B$3</f>
+        <f>SUM(S36:S39)*$B$3</f>
         <v/>
       </c>
     </row>
@@ -6200,95 +6206,100 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>(new)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Consumers — 2026 Pole Replacements</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="19">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Dec-27</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>WON — award $300K; EPC-paired $3.45M</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Total backlog remaining</t>
         </is>
       </c>
-      <c r="E14" s="24">
-        <f>SUM(E5:E13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="E15" s="24">
+        <f>SUM(E5:E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>PIPELINE — pending bids (CVR scope)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>CVR value</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Win prob.</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Expected award</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Frontier Make Ready</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Steuben County REMC</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E18" s="19">
-        <f>C18*D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Q3-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Jacksonburg–Gateway (EPC-paired $3.55M)</t>
+          <t>Frontier Make Ready</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Hoosier Energy</t>
+          <t>Steuben County REMC</t>
         </is>
       </c>
       <c r="C19" s="19" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>0.5</v>
@@ -6299,14 +6310,14 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Q4-26</t>
+          <t>Q3-26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Rosehill–Rockport (EPC-paired $5.59M)</t>
+          <t>Jacksonburg–Gateway (EPC-paired $3.55M)</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -6315,7 +6326,7 @@
         </is>
       </c>
       <c r="C20" s="19" t="n">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>0.5</v>
@@ -6333,16 +6344,16 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Joint Use Audit</t>
+          <t>Rosehill–Rockport (EPC-paired $5.59M)</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Lansing Board of Water &amp; Light</t>
+          <t>Hoosier Energy</t>
         </is>
       </c>
       <c r="C21" s="19" t="n">
-        <v>1350</v>
+        <v>290</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>0.5</v>
@@ -6360,19 +6371,19 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>2026 Pole Replacements (EPC-paired $3.45M)</t>
+          <t>Joint Use Audit</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Consumers Energy</t>
+          <t>Lansing Board of Water &amp; Light</t>
         </is>
       </c>
       <c r="C22" s="19" t="n">
-        <v>276</v>
+        <v>1350</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="E22" s="19">
         <f>C22*D22</f>
@@ -6418,7 +6429,7 @@
         </is>
       </c>
       <c r="E24" s="24">
-        <f>SUM(E18:E23)</f>
+        <f>SUM(E19:E23)</f>
         <v/>
       </c>
     </row>
@@ -6447,7 +6458,7 @@
         </is>
       </c>
       <c r="B28" s="19">
-        <f>E14+E24</f>
+        <f>E15+E24</f>
         <v/>
       </c>
     </row>
@@ -6878,7 +6889,7 @@
         </is>
       </c>
       <c r="B7" s="19">
-        <f>'Backlog &amp; Pipeline'!E14</f>
+        <f>'Backlog &amp; Pipeline'!E15</f>
         <v/>
       </c>
       <c r="C7" s="19" t="n">

--- a/model/CVR_Model_Phase2_Forecast.xlsx
+++ b/model/CVR_Model_Phase2_Forecast.xlsx
@@ -15,8 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash &amp; Note" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog &amp; Pipeline" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FY Summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Chart" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPC At-Scale Model" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Chart" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,11 +26,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0)"/>
+    <numFmt numFmtId="168" formatCode="$#,##0.00;($#,##0.00)"/>
+    <numFmt numFmtId="169" formatCode="0.0&quot;×&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -106,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,6 +138,13 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -711,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -862,29 +872,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Checks             — anchors to the GL baseline and internal integrity checks.</t>
+          <t xml:space="preserve">  EPC At-Scale Model — revised business model: CVR earns engineering + material margin on a $150M/yr EPC program</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Coverage Chart     — native chart: forecast line vs backlog + pipeline areas, with a 1/0 toggle</t>
+          <t xml:space="preserve">                       (steady-state illustration; HWC keeps equipment + labor margin).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Checks             — anchors to the GL baseline and internal integrity checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Coverage Chart     — native chart: forecast line vs backlog + pipeline areas, with a 1/0 toggle</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t xml:space="preserve">                       cell (B3) that includes or excludes the weighted pipeline live.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>COLOR KEY: blue = input · black = calculated · orange italics = assumption to confirm</t>
         </is>
@@ -896,6 +920,190 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Integrity checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>H1 revenue anchor ($K)</t>
+        </is>
+      </c>
+      <c r="B5" s="19">
+        <f>'FY Summary'!B5</f>
+        <v/>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>551</v>
+      </c>
+      <c r="D5" s="11">
+        <f>IF(ABS(B5-C5)&lt;=0.5,"TIES","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>H1 net income anchor ($K)</t>
+        </is>
+      </c>
+      <c r="B6" s="19">
+        <f>'FY Summary'!B9</f>
+        <v/>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>-320.5</v>
+      </c>
+      <c r="D6" s="11">
+        <f>IF(ABS(B6-C6)&lt;=0.5,"TIES","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Backlog remaining total ($K)</t>
+        </is>
+      </c>
+      <c r="B7" s="19">
+        <f>'Backlog &amp; Pipeline'!E15</f>
+        <v/>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>696.8</v>
+      </c>
+      <c r="D7" s="11">
+        <f>IF(ABS(B7-C7)&lt;=2.0,"TIES","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Note roll integrity: Dec-27 close = open − Σ op cash</t>
+        </is>
+      </c>
+      <c r="B8" s="19">
+        <f>'Cash &amp; Note'!S10</f>
+        <v/>
+      </c>
+      <c r="C8" s="19">
+        <f>3436.6-SUM('Cash &amp; Note'!B9:S9)</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>IF(ABS(B8-C8)&lt;=0.1,"TIES","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Coverage ratio computed</t>
+        </is>
+      </c>
+      <c r="B9" s="19">
+        <f>'Backlog &amp; Pipeline'!B28</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&gt;0 expected</t>
+        </is>
+      </c>
+      <c r="D9" s="11">
+        <f>IF(B9&gt;0,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>MODEL LIMITS (read before presenting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>• Revenue is capacity-driven; the coverage check disciplines it against booked work, but it is not a job-by-job burn schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Direct-charge share (92%) mirrors the GL convention; when salary detail arrives, split wages properly by person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• The FTE path assumes hires are productive in month one — add ramp months per hire if that proves optimistic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Pipeline probabilities are placeholders at the 2026 win rate (67%) or 50% — Estimating should own these numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Escalation is off (card rate and wages flat through 2027) — turn on via the scalar inputs when the 2027 rate sheet lands.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -937,7 +1145,7 @@
           <t>Coverage of forecast</t>
         </is>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="33">
         <f>(SUM(B35:S35)+SUM(B40:S40))/SUM(B41:S41)</f>
         <v/>
       </c>
@@ -948,7 +1156,7 @@
           <t>Gap to originate ($K)</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="34">
         <f>SUM(B41:S41)-SUM(B35:S35)-SUM(B40:S40)</f>
         <v/>
       </c>
@@ -6808,176 +7016,699 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="66" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Integrity checks</t>
+          <t>Revised Business Model — EPC at Scale: CVR earns engineering + material margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Steady-state illustration at $150M/yr EPC (NOT the near-term forecast). CVR takes engineering scope + material margin; HWC keeps equipment + labor margin. Blue = input; grey = calculated.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Expected</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>DRIVERS — edit the blue cells</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>H1 revenue anchor ($K)</t>
-        </is>
-      </c>
-      <c r="B5" s="19">
-        <f>'FY Summary'!B5</f>
-        <v/>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>551</v>
-      </c>
-      <c r="D5" s="11">
-        <f>IF(ABS(B5-C5)&lt;=0.5,"TIES","CHECK")</f>
-        <v/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EPC program volume ($M/yr)</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated EPC run-rate (HWC + CVR)</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>H1 net income anchor ($K)</t>
-        </is>
-      </c>
-      <c r="B6" s="19">
-        <f>'FY Summary'!B9</f>
-        <v/>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>-320.5</v>
-      </c>
-      <c r="D6" s="11">
-        <f>IF(ABS(B6-C6)&lt;=0.5,"TIES","CHECK")</f>
-        <v/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CVR materials share of EPC</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Materials through CVR; major equipment stays with HWC</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Backlog remaining total ($K)</t>
-        </is>
-      </c>
-      <c r="B7" s="19">
-        <f>'Backlog &amp; Pipeline'!E15</f>
-        <v/>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>696.8</v>
-      </c>
-      <c r="D7" s="11">
-        <f>IF(ABS(B7-C7)&lt;=2.0,"TIES","CHECK")</f>
-        <v/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Material gross margin</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CVR procurement markup on materials</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Note roll integrity: Dec-27 close = open − Σ op cash</t>
-        </is>
-      </c>
-      <c r="B8" s="19">
-        <f>'Cash &amp; Note'!S10</f>
-        <v/>
-      </c>
-      <c r="C8" s="19">
-        <f>3436.6-SUM('Cash &amp; Note'!B9:S9)</f>
-        <v/>
-      </c>
-      <c r="D8" s="11">
-        <f>IF(ABS(B8-C8)&lt;=0.1,"TIES","CHECK")</f>
-        <v/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Procurement + WC carry (pts of flow)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing staff + working-capital carry</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Coverage ratio computed</t>
-        </is>
-      </c>
-      <c r="B9" s="19">
-        <f>'Backlog &amp; Pipeline'!B28</f>
-        <v/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Engineering pull-through (% of EPC)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0.08</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>&gt;0 expected</t>
-        </is>
-      </c>
-      <c r="D9" s="11">
-        <f>IF(B9&gt;0,"OK","CHECK")</f>
-        <v/>
+          <t>CVR engineering scope at this scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Engineering gross margin</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Engineering revenue less direct labor</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>MODEL LIMITS (read before presenting)</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Engineering operating margin</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Engineering OI as % of eng revenue, at scale</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>• Revenue is capacity-driven; the coverage check disciplines it against booked work, but it is not a job-by-job burn schedule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Direct-charge share (92%) mirrors the GL convention; when salary detail arrives, split wages properly by person.</t>
+          <t>Working-capital carry (days of flow)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Days from paying suppliers to reimbursement</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• The FTE path assumes hires are productive in month one — add ramp months per hire if that proves optimistic.</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>MATERIAL PROCUREMENT — CVR as principal ($M)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>• Pipeline probabilities are placeholders at the 2026 win rate (67%) or 50% — Estimating should own these numbers.</t>
-        </is>
+          <t>Materials revenue (billed)</t>
+        </is>
+      </c>
+      <c r="B15" s="27">
+        <f>B5*B6</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Escalation is off (card rate and wages flat through 2027) — turn on via the scalar inputs when the 2027 rate sheet lands.</t>
+          <t>Materials cost (COGS, at cost)</t>
+        </is>
+      </c>
+      <c r="B16" s="27">
+        <f>B15*(1-B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Material gross margin</t>
+        </is>
+      </c>
+      <c r="B17" s="27">
+        <f>B15*B7</f>
+        <v/>
+      </c>
+      <c r="C17" s="28">
+        <f>B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Procurement + working-capital cost</t>
+        </is>
+      </c>
+      <c r="B18" s="27">
+        <f>B15*B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Material net contribution</t>
+        </is>
+      </c>
+      <c r="B19" s="29">
+        <f>B17-B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ENGINEERING SERVICES ($M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Engineering revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="27">
+        <f>B5*B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Engineering gross profit</t>
+        </is>
+      </c>
+      <c r="B23" s="27">
+        <f>B22*B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Engineering operating income</t>
+        </is>
+      </c>
+      <c r="B24" s="29">
+        <f>B22*B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Engineering OpEx (= GP − OI)</t>
+        </is>
+      </c>
+      <c r="B25" s="27">
+        <f>B23-B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>COMBINED CVR — STEADY STATE ($M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CVR revenue — gross / principal basis</t>
+        </is>
+      </c>
+      <c r="B28" s="27">
+        <f>B22+B15</f>
+        <v/>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>CVR takes title to materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>CVR revenue — managed-margin basis</t>
+        </is>
+      </c>
+      <c r="B29" s="29">
+        <f>B22+B17</f>
+        <v/>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>engineering + material margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CVR gross profit</t>
+        </is>
+      </c>
+      <c r="B30" s="27">
+        <f>B23+B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Total operating cost</t>
+        </is>
+      </c>
+      <c r="B31" s="27">
+        <f>B25+B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>CVR operating income (OILI)</t>
+        </is>
+      </c>
+      <c r="B32" s="30">
+        <f>B30-B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OI margin — managed revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="10">
+        <f>B32/B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OI margin — gross revenue</t>
+        </is>
+      </c>
+      <c r="B34" s="10">
+        <f>B32/B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working-capital requirement ($M)</t>
+        </is>
+      </c>
+      <c r="B35" s="27">
+        <f>B15*B12/365</f>
+        <v/>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>materials flow × carry days</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>CONTEXT vs TODAY &amp; THE YEAR-2 GOAL ($M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CVR revenue today (managed, ~FY26)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>current baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>This model — managed revenue</t>
+        </is>
+      </c>
+      <c r="B39" s="27">
+        <f>B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Year-2 goal operating profit ($6M × 20%)</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>This model — operating income</t>
+        </is>
+      </c>
+      <c r="B41" s="27">
+        <f>B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Multiple of the Year-2 goal profit</t>
+        </is>
+      </c>
+      <c r="B42" s="31">
+        <f>B32/B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>PER-PROJECT ILLUSTRATION — a $3.45M EPC job ($M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EPC job value</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Consumers-paired size</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Materials (share of job)</t>
+        </is>
+      </c>
+      <c r="B46" s="27">
+        <f>B45*B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CVR material margin</t>
+        </is>
+      </c>
+      <c r="B47" s="27">
+        <f>B46*B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CVR engineering scope</t>
+        </is>
+      </c>
+      <c r="B48" s="27">
+        <f>B45*B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>CVR total take on the job</t>
+        </is>
+      </c>
+      <c r="B49" s="29">
+        <f>B47+B48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CVR take as % of job value</t>
+        </is>
+      </c>
+      <c r="B50" s="10">
+        <f>B49/B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>vs engineering-only today ($0.30M)</t>
+        </is>
+      </c>
+      <c r="B51" s="27">
+        <f>B49-0.3</f>
+        <v/>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>uplift from adding material margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>SENSITIVITY — CVR operating income ($M): materials share × material margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>share ↓  /  margin →</t>
+        </is>
+      </c>
+      <c r="B54" s="32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C54" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D54" s="32" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E54" s="32" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B55" s="27">
+        <f>$B$5*$A55*(B$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="C55" s="27">
+        <f>$B$5*$A55*(C$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="D55" s="27">
+        <f>$B$5*$A55*(D$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="E55" s="27">
+        <f>$B$5*$A55*(E$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B56" s="27">
+        <f>$B$5*$A56*(B$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="C56" s="27">
+        <f>$B$5*$A56*(C$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="D56" s="27">
+        <f>$B$5*$A56*(D$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="E56" s="27">
+        <f>$B$5*$A56*(E$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="B57" s="27">
+        <f>$B$5*$A57*(B$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="C57" s="27">
+        <f>$B$5*$A57*(C$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="D57" s="30">
+        <f>$B$5*$A57*(D$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="E57" s="27">
+        <f>$B$5*$A57*(E$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B58" s="27">
+        <f>$B$5*$A58*(B$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="C58" s="27">
+        <f>$B$5*$A58*(C$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="D58" s="27">
+        <f>$B$5*$A58*(D$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="E58" s="27">
+        <f>$B$5*$A58*(E$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="B59" s="27">
+        <f>$B$5*$A59*(B$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="C59" s="27">
+        <f>$B$5*$A59*(C$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="D59" s="27">
+        <f>$B$5*$A59*(D$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+      <c r="E59" s="27">
+        <f>$B$5*$A59*(E$54-$B$8)+$B$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>• Steady-state at $150M/yr EPC — a future-state illustration, not the 18-month forecast. Reaching it depends on the EPC ramp (BD origination + HWC delivery capacity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>• Materials shown on a PRINCIPAL basis (CVR takes title): CVR recognizes ~$52.5M materials revenue and ~$45.7M COGS. On a managed-margin (agent) basis, CVR 'revenue' is engineering + material margin ≈ $18.8M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>• CVR carries material procurement and price/obsolescence risk plus ~$6.5M of working capital; the 2-pt carry cost is a placeholder — confirm payment terms and a financing line with USC/HWC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>• HWC retains equipment procurement and the labor/construction margin, so CVR participates in EPC economics without taking construction-execution risk.</t>
         </is>
       </c>
     </row>

--- a/model/CVR_Model_Phase2_Forecast.xlsx
+++ b/model/CVR_Model_Phase2_Forecast.xlsx
@@ -26,13 +26,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0)"/>
-    <numFmt numFmtId="168" formatCode="$#,##0.00;($#,##0.00)"/>
+    <numFmt numFmtId="168" formatCode="$#,##0.00"/>
     <numFmt numFmtId="169" formatCode="0.0&quot;×&quot;"/>
+    <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00)"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -109,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,12 +139,14 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1145,7 +1148,7 @@
           <t>Coverage of forecast</t>
         </is>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>(SUM(B35:S35)+SUM(B40:S40))/SUM(B41:S41)</f>
         <v/>
       </c>
@@ -1156,7 +1159,7 @@
           <t>Gap to originate ($K)</t>
         </is>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="36">
         <f>SUM(B41:S41)-SUM(B35:S35)-SUM(B40:S40)</f>
         <v/>
       </c>
@@ -6699,7 +6702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6999,7 +7002,65 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>AT-SCALE EPC MODEL (future state — see 'EPC At-Scale Model' tab), $M</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>CVR managed revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="26">
+        <f>'EPC At-Scale Model'!B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>CVR operating income (OILI)</t>
+        </is>
+      </c>
+      <c r="B23" s="27">
+        <f>'EPC At-Scale Model'!B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>OILI margin (managed)</t>
+        </is>
+      </c>
+      <c r="B24" s="10">
+        <f>'EPC At-Scale Model'!B33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Multiple of the $6M / 20% goal profit</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
+        <f>'EPC At-Scale Model'!B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>At-scale figures are $M and reflect $150M/yr EPC with CVR taking engineering + material margin (HWC keeps equipment + labor). A future-state target, not the FY27 forecast above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>The gap between FY27 forecast revenue and the $6M goal is structural (billable capacity), not effort: closing it requires the hiring ramp AND winning EPC-paired engineering at scale — see the utilization × realization grid in the Phase 1 workbook for the per-FTE ceiling math.</t>
         </is>
@@ -7054,7 +7115,7 @@
           <t>EPC program volume ($M/yr)</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="29" t="n">
         <v>150</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7181,7 +7242,7 @@
           <t>Materials revenue (billed)</t>
         </is>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="30">
         <f>B5*B6</f>
         <v/>
       </c>
@@ -7192,7 +7253,7 @@
           <t>Materials cost (COGS, at cost)</t>
         </is>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="30">
         <f>B15*(1-B7)</f>
         <v/>
       </c>
@@ -7203,11 +7264,11 @@
           <t>Material gross margin</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="30">
         <f>B15*B7</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="31">
         <f>B7</f>
         <v/>
       </c>
@@ -7218,7 +7279,7 @@
           <t>Procurement + working-capital cost</t>
         </is>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="30">
         <f>B15*B8</f>
         <v/>
       </c>
@@ -7229,7 +7290,7 @@
           <t>Material net contribution</t>
         </is>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="32">
         <f>B17-B18</f>
         <v/>
       </c>
@@ -7247,7 +7308,7 @@
           <t>Engineering revenue</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="30">
         <f>B5*B9</f>
         <v/>
       </c>
@@ -7258,7 +7319,7 @@
           <t>Engineering gross profit</t>
         </is>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="30">
         <f>B22*B10</f>
         <v/>
       </c>
@@ -7269,7 +7330,7 @@
           <t>Engineering operating income</t>
         </is>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="32">
         <f>B22*B11</f>
         <v/>
       </c>
@@ -7280,7 +7341,7 @@
           <t>Engineering OpEx (= GP − OI)</t>
         </is>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="30">
         <f>B23-B24</f>
         <v/>
       </c>
@@ -7298,7 +7359,7 @@
           <t>CVR revenue — gross / principal basis</t>
         </is>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="30">
         <f>B22+B15</f>
         <v/>
       </c>
@@ -7314,7 +7375,7 @@
           <t>CVR revenue — managed-margin basis</t>
         </is>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="32">
         <f>B22+B17</f>
         <v/>
       </c>
@@ -7330,7 +7391,7 @@
           <t>CVR gross profit</t>
         </is>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="30">
         <f>B23+B17</f>
         <v/>
       </c>
@@ -7341,7 +7402,7 @@
           <t>Total operating cost</t>
         </is>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="30">
         <f>B25+B18</f>
         <v/>
       </c>
@@ -7352,7 +7413,7 @@
           <t>CVR operating income (OILI)</t>
         </is>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="33">
         <f>B30-B31</f>
         <v/>
       </c>
@@ -7385,7 +7446,7 @@
           <t>Working-capital requirement ($M)</t>
         </is>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="30">
         <f>B15*B12/365</f>
         <v/>
       </c>
@@ -7408,7 +7469,7 @@
           <t>CVR revenue today (managed, ~FY26)</t>
         </is>
       </c>
-      <c r="B38" s="26" t="n">
+      <c r="B38" s="29" t="n">
         <v>1.42</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7423,7 +7484,7 @@
           <t>This model — managed revenue</t>
         </is>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="30">
         <f>B29</f>
         <v/>
       </c>
@@ -7434,7 +7495,7 @@
           <t>Year-2 goal operating profit ($6M × 20%)</t>
         </is>
       </c>
-      <c r="B40" s="26" t="n">
+      <c r="B40" s="29" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -7444,7 +7505,7 @@
           <t>This model — operating income</t>
         </is>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="30">
         <f>B32</f>
         <v/>
       </c>
@@ -7455,7 +7516,7 @@
           <t>Multiple of the Year-2 goal profit</t>
         </is>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="28">
         <f>B32/B40</f>
         <v/>
       </c>
@@ -7473,7 +7534,7 @@
           <t>EPC job value</t>
         </is>
       </c>
-      <c r="B45" s="26" t="n">
+      <c r="B45" s="29" t="n">
         <v>3.45</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -7488,7 +7549,7 @@
           <t>Materials (share of job)</t>
         </is>
       </c>
-      <c r="B46" s="27">
+      <c r="B46" s="30">
         <f>B45*B6</f>
         <v/>
       </c>
@@ -7499,7 +7560,7 @@
           <t>CVR material margin</t>
         </is>
       </c>
-      <c r="B47" s="27">
+      <c r="B47" s="30">
         <f>B46*B7</f>
         <v/>
       </c>
@@ -7510,7 +7571,7 @@
           <t>CVR engineering scope</t>
         </is>
       </c>
-      <c r="B48" s="27">
+      <c r="B48" s="30">
         <f>B45*B9</f>
         <v/>
       </c>
@@ -7521,7 +7582,7 @@
           <t>CVR total take on the job</t>
         </is>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="32">
         <f>B47+B48</f>
         <v/>
       </c>
@@ -7543,7 +7604,7 @@
           <t>vs engineering-only today ($0.30M)</t>
         </is>
       </c>
-      <c r="B51" s="27">
+      <c r="B51" s="30">
         <f>B49-0.3</f>
         <v/>
       </c>
@@ -7566,120 +7627,120 @@
           <t>share ↓  /  margin →</t>
         </is>
       </c>
-      <c r="B54" s="32" t="n">
+      <c r="B54" s="34" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C54" s="32" t="n">
+      <c r="C54" s="34" t="n">
         <v>0.1</v>
       </c>
-      <c r="D54" s="32" t="n">
+      <c r="D54" s="34" t="n">
         <v>0.13</v>
       </c>
-      <c r="E54" s="32" t="n">
+      <c r="E54" s="34" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="32" t="n">
+      <c r="A55" s="34" t="n">
         <v>0.25</v>
       </c>
-      <c r="B55" s="27">
+      <c r="B55" s="30">
         <f>$B$5*$A55*(B$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="30">
         <f>$B$5*$A55*(C$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="30">
         <f>$B$5*$A55*(D$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="E55" s="27">
+      <c r="E55" s="30">
         <f>$B$5*$A55*(E$54-$B$8)+$B$24</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="32" t="n">
+      <c r="A56" s="34" t="n">
         <v>0.3</v>
       </c>
-      <c r="B56" s="27">
+      <c r="B56" s="30">
         <f>$B$5*$A56*(B$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="30">
         <f>$B$5*$A56*(C$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="30">
         <f>$B$5*$A56*(D$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="E56" s="27">
+      <c r="E56" s="30">
         <f>$B$5*$A56*(E$54-$B$8)+$B$24</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="32" t="n">
+      <c r="A57" s="34" t="n">
         <v>0.35</v>
       </c>
-      <c r="B57" s="27">
+      <c r="B57" s="30">
         <f>$B$5*$A57*(B$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="30">
         <f>$B$5*$A57*(C$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="D57" s="30">
+      <c r="D57" s="33">
         <f>$B$5*$A57*(D$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="E57" s="27">
+      <c r="E57" s="30">
         <f>$B$5*$A57*(E$54-$B$8)+$B$24</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="n">
+      <c r="A58" s="34" t="n">
         <v>0.4</v>
       </c>
-      <c r="B58" s="27">
+      <c r="B58" s="30">
         <f>$B$5*$A58*(B$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="30">
         <f>$B$5*$A58*(C$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="D58" s="27">
+      <c r="D58" s="30">
         <f>$B$5*$A58*(D$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="E58" s="27">
+      <c r="E58" s="30">
         <f>$B$5*$A58*(E$54-$B$8)+$B$24</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="32" t="n">
+      <c r="A59" s="34" t="n">
         <v>0.45</v>
       </c>
-      <c r="B59" s="27">
+      <c r="B59" s="30">
         <f>$B$5*$A59*(B$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="30">
         <f>$B$5*$A59*(C$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="D59" s="27">
+      <c r="D59" s="30">
         <f>$B$5*$A59*(D$54-$B$8)+$B$24</f>
         <v/>
       </c>
-      <c r="E59" s="27">
+      <c r="E59" s="30">
         <f>$B$5*$A59*(E$54-$B$8)+$B$24</f>
         <v/>
       </c>

--- a/model/CVR_Model_Phase2_Forecast.xlsx
+++ b/model/CVR_Model_Phase2_Forecast.xlsx
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="19">
-        <f>'Backlog &amp; Pipeline'!B28</f>
+        <f>'Backlog &amp; Pipeline'!B29</f>
         <v/>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>• Pipeline probabilities are placeholders at the 2026 win rate (67%) or 50% — Estimating should own these numbers.</t>
+          <t>• Pipeline probabilities are placeholders at the 2026 win rate (69%) or 50% — Estimating should own these numbers.</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6087,7 +6087,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Backlog = remaining PO value on active jobs (KPI scorecard 7/11/26). Pipeline = pending bids × win probability.</t>
+          <t>Backlog = remaining PO value on active jobs (KPI scorecard 7/25/26). Pipeline = pending bids × win probability.</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="C14" s="19" t="n">
-        <v>300</v>
+        <v>276.45</v>
       </c>
       <c r="D14" s="19" t="n">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>WON — award $300K; EPC-paired $3.45M</t>
+          <t>WON — award $276K; EPC-paired $3.45M</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Renaissance 345kV Substation (ON HOLD)</t>
+          <t>Renaissance 345kV Substation (6 MOD switches)</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -6629,63 +6629,90 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>Sep-26 — in bid</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>VanMeter 161kV Substation (EPC-paired)</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>MEC (MidAmerican)</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="19">
+        <f>C24*D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Sep-26 — in bid</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Total probability-weighted pipeline</t>
         </is>
       </c>
-      <c r="E24" s="24">
-        <f>SUM(E19:E23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="E25" s="24">
+        <f>SUM(E19:E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>COVERAGE CHECK</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Forecast revenue, Jul-26 – Dec-27</t>
-        </is>
-      </c>
-      <c r="B27" s="19">
-        <f>'Forecast P&amp;L'!T6+'Forecast P&amp;L'!U6</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Booked + expected work (backlog + weighted pipeline)</t>
+          <t>Forecast revenue, Jul-26 – Dec-27</t>
         </is>
       </c>
       <c r="B28" s="19">
-        <f>E15+E24</f>
+        <f>'Forecast P&amp;L'!T6+'Forecast P&amp;L'!U6</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
+          <t>Booked + expected work (backlog + weighted pipeline)</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>E15+E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
           <t>Coverage ratio</t>
         </is>
       </c>
-      <c r="B29" s="10">
-        <f>B28/B27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="B30" s="10">
+        <f>B29/B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Coverage below 100% is normal at an 18-month horizon — the gap is work still to be won. But if coverage falls much below ~60%, the forecast is leaning on unidentified sales; treat the gap as the BD target: it quantifies how much new work Estimating must originate beyond the current bid list.</t>
         </is>
